--- a/AAII_Financials/Quarterly/AVAL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AVAL_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="92">
   <si>
     <t>AVAL</t>
   </si>
@@ -656,118 +656,124 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
-        <v>1760300</v>
+      <c r="D8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E8" s="3">
-        <v>1717100</v>
+        <v>1907000</v>
       </c>
       <c r="F8" s="3">
-        <v>1682000</v>
+        <v>1860200</v>
       </c>
       <c r="G8" s="3">
-        <v>1474500</v>
+        <v>1822200</v>
       </c>
       <c r="H8" s="3">
-        <v>1251100</v>
+        <v>1597300</v>
       </c>
       <c r="I8" s="3">
-        <v>1028800</v>
+        <v>1355400</v>
       </c>
       <c r="J8" s="3">
+        <v>1114500</v>
+      </c>
+      <c r="K8" s="3">
         <v>902300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>578700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>707300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>660300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>653500</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -810,8 +816,11 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -854,8 +863,11 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -872,8 +884,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -916,8 +929,11 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -960,8 +976,11 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -998,58 +1017,64 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>-69100</v>
+      <c r="D15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E15" s="3">
-        <v>-67800</v>
+        <v>-74800</v>
       </c>
       <c r="F15" s="3">
-        <v>-67100</v>
+        <v>-73500</v>
       </c>
       <c r="G15" s="3">
-        <v>-68600</v>
+        <v>-72700</v>
       </c>
       <c r="H15" s="3">
-        <v>-65000</v>
+        <v>-74300</v>
       </c>
       <c r="I15" s="3">
-        <v>-65000</v>
+        <v>-70400</v>
       </c>
       <c r="J15" s="3">
+        <v>-70400</v>
+      </c>
+      <c r="K15" s="3">
         <v>-63200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-62600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-57200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-52400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-52900</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1063,96 +1088,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>1649900</v>
+      <c r="D17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E17" s="3">
-        <v>1576200</v>
+        <v>1787400</v>
       </c>
       <c r="F17" s="3">
-        <v>1499000</v>
+        <v>1707500</v>
       </c>
       <c r="G17" s="3">
-        <v>1207500</v>
+        <v>1624000</v>
       </c>
       <c r="H17" s="3">
-        <v>929400</v>
+        <v>1308200</v>
       </c>
       <c r="I17" s="3">
-        <v>691000</v>
+        <v>1006800</v>
       </c>
       <c r="J17" s="3">
+        <v>748600</v>
+      </c>
+      <c r="K17" s="3">
         <v>569900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>251700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>364100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>387300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>404100</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>110400</v>
+      <c r="D18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E18" s="3">
-        <v>140900</v>
+        <v>119600</v>
       </c>
       <c r="F18" s="3">
-        <v>183000</v>
+        <v>152700</v>
       </c>
       <c r="G18" s="3">
-        <v>266900</v>
+        <v>198200</v>
       </c>
       <c r="H18" s="3">
-        <v>321700</v>
+        <v>289200</v>
       </c>
       <c r="I18" s="3">
-        <v>337800</v>
+        <v>348600</v>
       </c>
       <c r="J18" s="3">
+        <v>366000</v>
+      </c>
+      <c r="K18" s="3">
         <v>332400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>326900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>343200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>273000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>249400</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1169,96 +1201,103 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>4000</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E20" s="3">
-        <v>53700</v>
+        <v>4400</v>
       </c>
       <c r="F20" s="3">
-        <v>196200</v>
+        <v>58200</v>
       </c>
       <c r="G20" s="3">
-        <v>-67700</v>
+        <v>212500</v>
       </c>
       <c r="H20" s="3">
-        <v>32900</v>
+        <v>-73300</v>
       </c>
       <c r="I20" s="3">
-        <v>130300</v>
+        <v>35600</v>
       </c>
       <c r="J20" s="3">
+        <v>141100</v>
+      </c>
+      <c r="K20" s="3">
         <v>151400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-32600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>58500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>91300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>81900</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>183500</v>
+      <c r="D21" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E21" s="3">
-        <v>262500</v>
+        <v>198800</v>
       </c>
       <c r="F21" s="3">
-        <v>446300</v>
+        <v>284400</v>
       </c>
       <c r="G21" s="3">
-        <v>267800</v>
+        <v>483400</v>
       </c>
       <c r="H21" s="3">
-        <v>419600</v>
+        <v>290200</v>
       </c>
       <c r="I21" s="3">
-        <v>533100</v>
+        <v>454600</v>
       </c>
       <c r="J21" s="3">
+        <v>577500</v>
+      </c>
+      <c r="K21" s="3">
         <v>547100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>383500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>482300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>438200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>406100</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1295,102 +1334,111 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
+      <c r="O22" s="3">
+        <v>0</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>114500</v>
+        <v>161100</v>
       </c>
       <c r="E23" s="3">
-        <v>194700</v>
+        <v>124000</v>
       </c>
       <c r="F23" s="3">
-        <v>379200</v>
+        <v>210900</v>
       </c>
       <c r="G23" s="3">
-        <v>199300</v>
+        <v>410700</v>
       </c>
       <c r="H23" s="3">
-        <v>354600</v>
+        <v>215900</v>
       </c>
       <c r="I23" s="3">
-        <v>468100</v>
+        <v>384200</v>
       </c>
       <c r="J23" s="3">
+        <v>507100</v>
+      </c>
+      <c r="K23" s="3">
         <v>483900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>294300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>401700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>364300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>331300</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>42300</v>
+        <v>65300</v>
       </c>
       <c r="E24" s="3">
-        <v>84100</v>
+        <v>45800</v>
       </c>
       <c r="F24" s="3">
-        <v>127800</v>
+        <v>91100</v>
       </c>
       <c r="G24" s="3">
-        <v>126300</v>
+        <v>138500</v>
       </c>
       <c r="H24" s="3">
-        <v>131500</v>
+        <v>136800</v>
       </c>
       <c r="I24" s="3">
-        <v>135400</v>
+        <v>142400</v>
       </c>
       <c r="J24" s="3">
+        <v>146700</v>
+      </c>
+      <c r="K24" s="3">
         <v>151900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>91000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>222600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>92500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>103300</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1433,96 +1481,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>72200</v>
+      <c r="D26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E26" s="3">
-        <v>110500</v>
+        <v>78200</v>
       </c>
       <c r="F26" s="3">
-        <v>251300</v>
+        <v>119800</v>
       </c>
       <c r="G26" s="3">
-        <v>72900</v>
+        <v>272300</v>
       </c>
       <c r="H26" s="3">
-        <v>223100</v>
+        <v>79000</v>
       </c>
       <c r="I26" s="3">
-        <v>332700</v>
+        <v>241700</v>
       </c>
       <c r="J26" s="3">
+        <v>360400</v>
+      </c>
+      <c r="K26" s="3">
         <v>332000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>203300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>179100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>271800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>228000</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>15600</v>
+      <c r="D27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E27" s="3">
-        <v>39900</v>
+        <v>16800</v>
       </c>
       <c r="F27" s="3">
-        <v>102000</v>
+        <v>43200</v>
       </c>
       <c r="G27" s="3">
-        <v>95700</v>
+        <v>110500</v>
       </c>
       <c r="H27" s="3">
-        <v>97900</v>
+        <v>103700</v>
       </c>
       <c r="I27" s="3">
-        <v>162100</v>
+        <v>106100</v>
       </c>
       <c r="J27" s="3">
+        <v>175600</v>
+      </c>
+      <c r="K27" s="3">
         <v>151600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>37000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>111600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>138700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>204000</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1565,8 +1622,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1576,41 +1636,44 @@
       <c r="E29" s="3">
         <v>0</v>
       </c>
-      <c r="F29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G29" s="3">
-        <v>-198200</v>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>-214700</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>263500</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-73000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>59900</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>60700</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-37700</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1653,8 +1716,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1697,96 +1763,105 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-4000</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E32" s="3">
-        <v>-53700</v>
+        <v>-4400</v>
       </c>
       <c r="F32" s="3">
-        <v>-196200</v>
+        <v>-58200</v>
       </c>
       <c r="G32" s="3">
-        <v>67700</v>
+        <v>-212500</v>
       </c>
       <c r="H32" s="3">
-        <v>-32900</v>
+        <v>73300</v>
       </c>
       <c r="I32" s="3">
-        <v>-130300</v>
+        <v>-35600</v>
       </c>
       <c r="J32" s="3">
+        <v>-141100</v>
+      </c>
+      <c r="K32" s="3">
         <v>-151400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>32600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-58500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-91300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-81900</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>15600</v>
+      <c r="D33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E33" s="3">
-        <v>39900</v>
+        <v>16800</v>
       </c>
       <c r="F33" s="3">
-        <v>102000</v>
+        <v>43200</v>
       </c>
       <c r="G33" s="3">
-        <v>-102500</v>
+        <v>110500</v>
       </c>
       <c r="H33" s="3">
-        <v>97900</v>
+        <v>-111000</v>
       </c>
       <c r="I33" s="3">
-        <v>162100</v>
+        <v>106100</v>
       </c>
       <c r="J33" s="3">
+        <v>175600</v>
+      </c>
+      <c r="K33" s="3">
         <v>415100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-36100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>171500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>199400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>166300</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1829,101 +1904,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>15600</v>
+      <c r="D35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E35" s="3">
-        <v>39900</v>
+        <v>16800</v>
       </c>
       <c r="F35" s="3">
-        <v>102000</v>
+        <v>43200</v>
       </c>
       <c r="G35" s="3">
-        <v>-102500</v>
+        <v>110500</v>
       </c>
       <c r="H35" s="3">
-        <v>97900</v>
+        <v>-111000</v>
       </c>
       <c r="I35" s="3">
-        <v>162100</v>
+        <v>106100</v>
       </c>
       <c r="J35" s="3">
+        <v>175600</v>
+      </c>
+      <c r="K35" s="3">
         <v>415100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-36100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>171500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>199400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>166300</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1940,8 +2024,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1958,96 +2043,103 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
-        <v>4411700</v>
+      <c r="D41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E41" s="3">
-        <v>4607000</v>
+        <v>4779400</v>
       </c>
       <c r="F41" s="3">
-        <v>4638700</v>
+        <v>4990900</v>
       </c>
       <c r="G41" s="3">
-        <v>4087900</v>
+        <v>5025200</v>
       </c>
       <c r="H41" s="3">
-        <v>4323300</v>
+        <v>4428500</v>
       </c>
       <c r="I41" s="3">
-        <v>5145900</v>
+        <v>4683600</v>
       </c>
       <c r="J41" s="3">
+        <v>5574700</v>
+      </c>
+      <c r="K41" s="3">
         <v>3937700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8794300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7896300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7478900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7377700</v>
       </c>
-      <c r="O41" s="3">
-        <v>0</v>
-      </c>
       <c r="P41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>11203700</v>
+        <v>12980600</v>
       </c>
       <c r="E42" s="3">
-        <v>11077200</v>
+        <v>12137300</v>
       </c>
       <c r="F42" s="3">
-        <v>10941500</v>
+        <v>12000300</v>
       </c>
       <c r="G42" s="3">
-        <v>10928800</v>
+        <v>11853300</v>
       </c>
       <c r="H42" s="3">
-        <v>10584600</v>
+        <v>11839600</v>
       </c>
       <c r="I42" s="3">
-        <v>10230700</v>
+        <v>11466600</v>
       </c>
       <c r="J42" s="3">
+        <v>11083300</v>
+      </c>
+      <c r="K42" s="3">
         <v>9948200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>13366900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>11815200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>11196400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>10964900</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2090,8 +2182,11 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2134,8 +2229,11 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2178,8 +2276,11 @@
       <c r="P45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2222,140 +2323,152 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>300100</v>
+        <v>335600</v>
       </c>
       <c r="E47" s="3">
-        <v>290700</v>
+        <v>325200</v>
       </c>
       <c r="F47" s="3">
-        <v>285900</v>
+        <v>315000</v>
       </c>
       <c r="G47" s="3">
-        <v>341600</v>
+        <v>309800</v>
       </c>
       <c r="H47" s="3">
-        <v>1318500</v>
+        <v>370100</v>
       </c>
       <c r="I47" s="3">
-        <v>1171700</v>
+        <v>1428400</v>
       </c>
       <c r="J47" s="3">
+        <v>1269300</v>
+      </c>
+      <c r="K47" s="3">
         <v>1045700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>281500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>236900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>222000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>203600</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1689300</v>
+        <v>1818900</v>
       </c>
       <c r="E48" s="3">
-        <v>1707300</v>
+        <v>1830100</v>
       </c>
       <c r="F48" s="3">
-        <v>1739500</v>
+        <v>1849500</v>
       </c>
       <c r="G48" s="3">
-        <v>1736500</v>
+        <v>1884400</v>
       </c>
       <c r="H48" s="3">
-        <v>1710200</v>
+        <v>1881200</v>
       </c>
       <c r="I48" s="3">
-        <v>1690500</v>
+        <v>1852700</v>
       </c>
       <c r="J48" s="3">
+        <v>1831400</v>
+      </c>
+      <c r="K48" s="3">
         <v>1680800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2184100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1943400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1863500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1891300</v>
       </c>
-      <c r="O48" s="3">
-        <v>0</v>
-      </c>
       <c r="P48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>4330700</v>
+        <v>4716900</v>
       </c>
       <c r="E49" s="3">
-        <v>4308000</v>
+        <v>4691600</v>
       </c>
       <c r="F49" s="3">
-        <v>4284300</v>
+        <v>4667000</v>
       </c>
       <c r="G49" s="3">
-        <v>4207500</v>
+        <v>4641300</v>
       </c>
       <c r="H49" s="3">
-        <v>4029400</v>
+        <v>4558100</v>
       </c>
       <c r="I49" s="3">
-        <v>3848700</v>
+        <v>4365200</v>
       </c>
       <c r="J49" s="3">
+        <v>4169400</v>
+      </c>
+      <c r="K49" s="3">
         <v>3659200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5153000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4526400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4199400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4064600</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
-      </c>
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2398,8 +2511,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2442,52 +2558,58 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>22600</v>
+        <v>359300</v>
       </c>
       <c r="E52" s="3">
-        <v>28200</v>
+        <v>24500</v>
       </c>
       <c r="F52" s="3">
-        <v>24000</v>
+        <v>30600</v>
       </c>
       <c r="G52" s="3">
-        <v>466600</v>
+        <v>26000</v>
       </c>
       <c r="H52" s="3">
-        <v>33000</v>
+        <v>505500</v>
       </c>
       <c r="I52" s="3">
-        <v>34800</v>
+        <v>35800</v>
       </c>
       <c r="J52" s="3">
+        <v>37700</v>
+      </c>
+      <c r="K52" s="3">
         <v>35300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>473700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>31700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>26300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>52600</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
       <c r="P52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2530,52 +2652,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
-        <v>71695800</v>
+      <c r="D54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E54" s="3">
-        <v>71534800</v>
+        <v>77670400</v>
       </c>
       <c r="F54" s="3">
-        <v>71730800</v>
+        <v>77496000</v>
       </c>
       <c r="G54" s="3">
-        <v>70941900</v>
+        <v>77708300</v>
       </c>
       <c r="H54" s="3">
-        <v>68615100</v>
+        <v>76853700</v>
       </c>
       <c r="I54" s="3">
-        <v>66266600</v>
+        <v>74333000</v>
       </c>
       <c r="J54" s="3">
+        <v>71788900</v>
+      </c>
+      <c r="K54" s="3">
         <v>62669800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>88056900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>77375100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>72292900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>70751400</v>
       </c>
-      <c r="O54" s="3">
-        <v>0</v>
-      </c>
       <c r="P54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2592,8 +2720,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2610,52 +2739,56 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>658900</v>
+      <c r="D57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E57" s="3">
-        <v>656900</v>
+        <v>713800</v>
       </c>
       <c r="F57" s="3">
-        <v>662300</v>
+        <v>711600</v>
       </c>
       <c r="G57" s="3">
-        <v>672900</v>
+        <v>717500</v>
       </c>
       <c r="H57" s="3">
-        <v>614500</v>
+        <v>729000</v>
       </c>
       <c r="I57" s="3">
-        <v>612800</v>
+        <v>665700</v>
       </c>
       <c r="J57" s="3">
+        <v>663800</v>
+      </c>
+      <c r="K57" s="3">
         <v>569900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>774800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>641300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>596400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>572900</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
       <c r="P57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2698,52 +2831,58 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1742500</v>
+        <v>69800</v>
       </c>
       <c r="E59" s="3">
-        <v>1830300</v>
+        <v>1887700</v>
       </c>
       <c r="F59" s="3">
-        <v>1964500</v>
+        <v>1982800</v>
       </c>
       <c r="G59" s="3">
-        <v>224300</v>
+        <v>2128200</v>
       </c>
       <c r="H59" s="3">
-        <v>1403700</v>
+        <v>243000</v>
       </c>
       <c r="I59" s="3">
-        <v>1317200</v>
+        <v>1520600</v>
       </c>
       <c r="J59" s="3">
+        <v>1427000</v>
+      </c>
+      <c r="K59" s="3">
         <v>1298500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>387400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1382400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1246800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1332200</v>
       </c>
-      <c r="O59" s="3">
-        <v>0</v>
-      </c>
       <c r="P59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2786,96 +2925,105 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>12757700</v>
+        <v>13119400</v>
       </c>
       <c r="E61" s="3">
-        <v>12831400</v>
+        <v>13820800</v>
       </c>
       <c r="F61" s="3">
-        <v>14697300</v>
+        <v>13900700</v>
       </c>
       <c r="G61" s="3">
-        <v>15126900</v>
+        <v>15922100</v>
       </c>
       <c r="H61" s="3">
-        <v>14172800</v>
+        <v>16387500</v>
       </c>
       <c r="I61" s="3">
-        <v>13956900</v>
+        <v>15353900</v>
       </c>
       <c r="J61" s="3">
+        <v>15120000</v>
+      </c>
+      <c r="K61" s="3">
         <v>12389300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>15026400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>12193300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>11352000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>11073300</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>353700</v>
+        <v>1959800</v>
       </c>
       <c r="E62" s="3">
-        <v>363800</v>
+        <v>383200</v>
       </c>
       <c r="F62" s="3">
-        <v>385000</v>
+        <v>394200</v>
       </c>
       <c r="G62" s="3">
-        <v>1621000</v>
+        <v>417100</v>
       </c>
       <c r="H62" s="3">
-        <v>375300</v>
+        <v>1756100</v>
       </c>
       <c r="I62" s="3">
-        <v>373500</v>
+        <v>406600</v>
       </c>
       <c r="J62" s="3">
+        <v>404600</v>
+      </c>
+      <c r="K62" s="3">
         <v>393900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1462300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>348700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>332700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>339500</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
       <c r="P62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2918,8 +3066,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2962,8 +3113,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3006,52 +3160,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>67764200</v>
+        <v>73943700</v>
       </c>
       <c r="E66" s="3">
-        <v>67583100</v>
+        <v>73411200</v>
       </c>
       <c r="F66" s="3">
-        <v>67848600</v>
+        <v>73215000</v>
       </c>
       <c r="G66" s="3">
-        <v>66989800</v>
+        <v>73502600</v>
       </c>
       <c r="H66" s="3">
-        <v>64591100</v>
+        <v>72572300</v>
       </c>
       <c r="I66" s="3">
-        <v>62325900</v>
+        <v>69973700</v>
       </c>
       <c r="J66" s="3">
+        <v>67519700</v>
+      </c>
+      <c r="K66" s="3">
         <v>58774500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>82533700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>72460600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>67787200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>66472500</v>
       </c>
-      <c r="O66" s="3">
-        <v>0</v>
-      </c>
       <c r="P66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3068,8 +3228,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3112,8 +3273,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3156,8 +3320,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3200,8 +3367,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3244,52 +3414,58 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1834000</v>
+        <v>2010300</v>
       </c>
       <c r="E72" s="3">
-        <v>1820300</v>
+        <v>1986800</v>
       </c>
       <c r="F72" s="3">
-        <v>1782800</v>
+        <v>1972000</v>
       </c>
       <c r="G72" s="3">
-        <v>1924400</v>
+        <v>1931400</v>
       </c>
       <c r="H72" s="3">
-        <v>2004200</v>
+        <v>2084800</v>
       </c>
       <c r="I72" s="3">
-        <v>1906600</v>
+        <v>2171200</v>
       </c>
       <c r="J72" s="3">
+        <v>2065500</v>
+      </c>
+      <c r="K72" s="3">
         <v>2032800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3212000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2777700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2486200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2287600</v>
       </c>
-      <c r="O72" s="3">
-        <v>0</v>
-      </c>
       <c r="P72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3332,8 +3508,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3376,8 +3555,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3420,52 +3602,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>3931600</v>
+        <v>4363500</v>
       </c>
       <c r="E76" s="3">
-        <v>3951700</v>
+        <v>4259200</v>
       </c>
       <c r="F76" s="3">
-        <v>3882200</v>
+        <v>4281000</v>
       </c>
       <c r="G76" s="3">
-        <v>3952100</v>
+        <v>4205700</v>
       </c>
       <c r="H76" s="3">
-        <v>4024000</v>
+        <v>4281400</v>
       </c>
       <c r="I76" s="3">
-        <v>3940800</v>
+        <v>4359300</v>
       </c>
       <c r="J76" s="3">
+        <v>4269200</v>
+      </c>
+      <c r="K76" s="3">
         <v>3895300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5523300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4914500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4505700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4279000</v>
       </c>
-      <c r="O76" s="3">
-        <v>0</v>
-      </c>
       <c r="P76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3508,101 +3696,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>15600</v>
+      <c r="D81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E81" s="3">
-        <v>39900</v>
+        <v>16800</v>
       </c>
       <c r="F81" s="3">
-        <v>102000</v>
+        <v>43200</v>
       </c>
       <c r="G81" s="3">
-        <v>-102500</v>
+        <v>110500</v>
       </c>
       <c r="H81" s="3">
-        <v>97900</v>
+        <v>-111000</v>
       </c>
       <c r="I81" s="3">
-        <v>162100</v>
+        <v>106100</v>
       </c>
       <c r="J81" s="3">
+        <v>175600</v>
+      </c>
+      <c r="K81" s="3">
         <v>415100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-36100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>171500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>199400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>166300</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3619,52 +3816,56 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>69100</v>
+      <c r="D83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E83" s="3">
-        <v>67800</v>
+        <v>74800</v>
       </c>
       <c r="F83" s="3">
-        <v>67100</v>
+        <v>73500</v>
       </c>
       <c r="G83" s="3">
-        <v>68600</v>
+        <v>72700</v>
       </c>
       <c r="H83" s="3">
-        <v>65000</v>
+        <v>74300</v>
       </c>
       <c r="I83" s="3">
-        <v>65000</v>
+        <v>70400</v>
       </c>
       <c r="J83" s="3">
+        <v>70400</v>
+      </c>
+      <c r="K83" s="3">
         <v>63200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>89100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>80700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>73900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>74800</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
       <c r="P83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3707,8 +3908,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3751,8 +3955,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3795,8 +4002,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3839,8 +4049,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3883,52 +4096,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>292200</v>
+      <c r="D89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E89" s="3">
-        <v>297600</v>
+        <v>316600</v>
       </c>
       <c r="F89" s="3">
-        <v>173300</v>
+        <v>322400</v>
       </c>
       <c r="G89" s="3">
-        <v>-998500</v>
+        <v>187800</v>
       </c>
       <c r="H89" s="3">
-        <v>-319700</v>
+        <v>-1081700</v>
       </c>
       <c r="I89" s="3">
-        <v>1419700</v>
+        <v>-346300</v>
       </c>
       <c r="J89" s="3">
+        <v>1538000</v>
+      </c>
+      <c r="K89" s="3">
         <v>-489300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>495500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-21700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>505500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>321100</v>
       </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
       <c r="P89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3945,52 +4164,56 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-147628000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-394006000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-257519000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-205678000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-482508000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-281054000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-238582000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-143769000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-489803000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-299606000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-24200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-16300</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4033,8 +4256,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4077,52 +4303,58 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>-222200</v>
+      <c r="D94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E94" s="3">
-        <v>55000</v>
+        <v>-240700</v>
       </c>
       <c r="F94" s="3">
-        <v>626900</v>
+        <v>59600</v>
       </c>
       <c r="G94" s="3">
-        <v>662200</v>
+        <v>679100</v>
       </c>
       <c r="H94" s="3">
-        <v>332000</v>
+        <v>717400</v>
       </c>
       <c r="I94" s="3">
-        <v>44200</v>
+        <v>359600</v>
       </c>
       <c r="J94" s="3">
+        <v>47900</v>
+      </c>
+      <c r="K94" s="3">
         <v>-4161400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-522800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>67100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-178900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-814100</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4139,52 +4371,56 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-61200</v>
+        <v>-66300</v>
       </c>
       <c r="E96" s="3">
-        <v>-61200</v>
+        <v>-66300</v>
       </c>
       <c r="F96" s="3">
+        <v>-66300</v>
+      </c>
+      <c r="G96" s="3">
         <v>-400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-500</v>
       </c>
-      <c r="H96" s="3">
-        <v>-600</v>
-      </c>
       <c r="I96" s="3">
-        <v>-26400</v>
+        <v>-700</v>
       </c>
       <c r="J96" s="3">
+        <v>-28600</v>
+      </c>
+      <c r="K96" s="3">
         <v>-72000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-72100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-66000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-62900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-69500</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4227,8 +4463,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4271,8 +4510,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4315,136 +4557,148 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-232700</v>
+        <v>-269100</v>
       </c>
       <c r="E100" s="3">
-        <v>-210300</v>
+        <v>-252100</v>
       </c>
       <c r="F100" s="3">
-        <v>-157400</v>
+        <v>-227900</v>
       </c>
       <c r="G100" s="3">
-        <v>-573100</v>
+        <v>-170500</v>
       </c>
       <c r="H100" s="3">
-        <v>-1139200</v>
+        <v>-620900</v>
       </c>
       <c r="I100" s="3">
-        <v>-254900</v>
+        <v>-1234200</v>
       </c>
       <c r="J100" s="3">
+        <v>-276100</v>
+      </c>
+      <c r="K100" s="3">
         <v>-89700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-18500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-57600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-229100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>17700</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-32500</v>
+        <v>-390100</v>
       </c>
       <c r="E101" s="3">
-        <v>-174000</v>
+        <v>-35200</v>
       </c>
       <c r="F101" s="3">
-        <v>-92100</v>
+        <v>-188500</v>
       </c>
       <c r="G101" s="3">
-        <v>673900</v>
+        <v>-99800</v>
       </c>
       <c r="H101" s="3">
-        <v>304400</v>
+        <v>730100</v>
       </c>
       <c r="I101" s="3">
-        <v>-900</v>
+        <v>329800</v>
       </c>
       <c r="J101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="K101" s="3">
         <v>-116100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>226000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>73500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>3600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>707700</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-195200</v>
+        <v>56100</v>
       </c>
       <c r="E102" s="3">
-        <v>-31700</v>
+        <v>-211500</v>
       </c>
       <c r="F102" s="3">
-        <v>550800</v>
+        <v>-34400</v>
       </c>
       <c r="G102" s="3">
-        <v>-235500</v>
+        <v>596700</v>
       </c>
       <c r="H102" s="3">
-        <v>-822500</v>
+        <v>-255100</v>
       </c>
       <c r="I102" s="3">
-        <v>1208200</v>
+        <v>-891100</v>
       </c>
       <c r="J102" s="3">
+        <v>1308800</v>
+      </c>
+      <c r="K102" s="3">
         <v>-4856600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>180100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>61300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>101100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>232400</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AVAL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AVAL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="92">
   <si>
     <t>AVAL</t>
   </si>
@@ -656,124 +656,130 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
+      <c r="D8" s="3">
+        <v>1809000</v>
       </c>
       <c r="E8" s="3">
-        <v>1907000</v>
+        <v>1855500</v>
       </c>
       <c r="F8" s="3">
-        <v>1860200</v>
+        <v>1833700</v>
       </c>
       <c r="G8" s="3">
-        <v>1822200</v>
+        <v>1788600</v>
       </c>
       <c r="H8" s="3">
-        <v>1597300</v>
+        <v>1752100</v>
       </c>
       <c r="I8" s="3">
-        <v>1355400</v>
+        <v>1535900</v>
       </c>
       <c r="J8" s="3">
+        <v>1303200</v>
+      </c>
+      <c r="K8" s="3">
         <v>1114500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>902300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>578700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>707300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>660300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>653500</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -819,8 +825,11 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -866,8 +875,11 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -885,8 +897,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -932,8 +945,11 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -979,8 +995,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1020,61 +1039,67 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>3</v>
+      <c r="D15" s="3">
+        <v>-75500</v>
       </c>
       <c r="E15" s="3">
-        <v>-74800</v>
+        <v>-75300</v>
       </c>
       <c r="F15" s="3">
-        <v>-73500</v>
+        <v>-72000</v>
       </c>
       <c r="G15" s="3">
-        <v>-72700</v>
+        <v>-70600</v>
       </c>
       <c r="H15" s="3">
-        <v>-74300</v>
+        <v>-69900</v>
       </c>
       <c r="I15" s="3">
+        <v>-71400</v>
+      </c>
+      <c r="J15" s="3">
+        <v>-67700</v>
+      </c>
+      <c r="K15" s="3">
         <v>-70400</v>
       </c>
-      <c r="J15" s="3">
-        <v>-70400</v>
-      </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-63200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-62600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-57200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-52400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-52900</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1089,102 +1114,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>3</v>
+      <c r="D17" s="3">
+        <v>1729000</v>
       </c>
       <c r="E17" s="3">
-        <v>1787400</v>
+        <v>1781700</v>
       </c>
       <c r="F17" s="3">
-        <v>1707500</v>
+        <v>1718600</v>
       </c>
       <c r="G17" s="3">
-        <v>1624000</v>
+        <v>1641800</v>
       </c>
       <c r="H17" s="3">
-        <v>1308200</v>
+        <v>1561500</v>
       </c>
       <c r="I17" s="3">
-        <v>1006800</v>
+        <v>1257900</v>
       </c>
       <c r="J17" s="3">
+        <v>968100</v>
+      </c>
+      <c r="K17" s="3">
         <v>748600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>569900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>251700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>364100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>387300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>404100</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>80100</v>
       </c>
       <c r="E18" s="3">
-        <v>119600</v>
+        <v>73700</v>
       </c>
       <c r="F18" s="3">
-        <v>152700</v>
+        <v>115000</v>
       </c>
       <c r="G18" s="3">
-        <v>198200</v>
+        <v>146800</v>
       </c>
       <c r="H18" s="3">
-        <v>289200</v>
+        <v>190600</v>
       </c>
       <c r="I18" s="3">
-        <v>348600</v>
+        <v>278000</v>
       </c>
       <c r="J18" s="3">
+        <v>335100</v>
+      </c>
+      <c r="K18" s="3">
         <v>366000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>332400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>326900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>343200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>273000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>249400</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1202,102 +1234,109 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>94700</v>
       </c>
       <c r="E20" s="3">
-        <v>4400</v>
+        <v>81200</v>
       </c>
       <c r="F20" s="3">
-        <v>58200</v>
+        <v>4200</v>
       </c>
       <c r="G20" s="3">
-        <v>212500</v>
+        <v>56000</v>
       </c>
       <c r="H20" s="3">
-        <v>-73300</v>
+        <v>204400</v>
       </c>
       <c r="I20" s="3">
-        <v>35600</v>
+        <v>-70500</v>
       </c>
       <c r="J20" s="3">
+        <v>34200</v>
+      </c>
+      <c r="K20" s="3">
         <v>141100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>151400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-32600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>58500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>91300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>81900</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>250300</v>
       </c>
       <c r="E21" s="3">
-        <v>198800</v>
+        <v>230200</v>
       </c>
       <c r="F21" s="3">
-        <v>284400</v>
+        <v>191200</v>
       </c>
       <c r="G21" s="3">
-        <v>483400</v>
+        <v>273400</v>
       </c>
       <c r="H21" s="3">
-        <v>290200</v>
+        <v>464800</v>
       </c>
       <c r="I21" s="3">
-        <v>454600</v>
+        <v>279000</v>
       </c>
       <c r="J21" s="3">
+        <v>437100</v>
+      </c>
+      <c r="K21" s="3">
         <v>577500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>547100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>383500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>482300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>438200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>406100</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1337,108 +1376,117 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
+      <c r="P22" s="3">
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>161100</v>
+        <v>174700</v>
       </c>
       <c r="E23" s="3">
-        <v>124000</v>
+        <v>154900</v>
       </c>
       <c r="F23" s="3">
-        <v>210900</v>
+        <v>119200</v>
       </c>
       <c r="G23" s="3">
-        <v>410700</v>
+        <v>202800</v>
       </c>
       <c r="H23" s="3">
-        <v>215900</v>
+        <v>395000</v>
       </c>
       <c r="I23" s="3">
-        <v>384200</v>
+        <v>207600</v>
       </c>
       <c r="J23" s="3">
+        <v>369400</v>
+      </c>
+      <c r="K23" s="3">
         <v>507100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>483900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>294300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>401700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>364300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>331300</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>65300</v>
+        <v>56400</v>
       </c>
       <c r="E24" s="3">
-        <v>45800</v>
+        <v>62800</v>
       </c>
       <c r="F24" s="3">
-        <v>91100</v>
+        <v>44100</v>
       </c>
       <c r="G24" s="3">
-        <v>138500</v>
+        <v>87600</v>
       </c>
       <c r="H24" s="3">
-        <v>136800</v>
+        <v>133100</v>
       </c>
       <c r="I24" s="3">
-        <v>142400</v>
+        <v>131600</v>
       </c>
       <c r="J24" s="3">
+        <v>137000</v>
+      </c>
+      <c r="K24" s="3">
         <v>146700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>151900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>91000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>222600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>92500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>103300</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1484,102 +1532,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>3</v>
+      <c r="D26" s="3">
+        <v>118300</v>
       </c>
       <c r="E26" s="3">
-        <v>78200</v>
+        <v>92100</v>
       </c>
       <c r="F26" s="3">
-        <v>119800</v>
+        <v>75200</v>
       </c>
       <c r="G26" s="3">
-        <v>272300</v>
+        <v>115100</v>
       </c>
       <c r="H26" s="3">
-        <v>79000</v>
+        <v>261800</v>
       </c>
       <c r="I26" s="3">
-        <v>241700</v>
+        <v>76000</v>
       </c>
       <c r="J26" s="3">
+        <v>232400</v>
+      </c>
+      <c r="K26" s="3">
         <v>360400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>332000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>203300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>179100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>271800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>228000</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>3</v>
+      <c r="D27" s="3">
+        <v>28400</v>
       </c>
       <c r="E27" s="3">
-        <v>16800</v>
+        <v>195500</v>
       </c>
       <c r="F27" s="3">
-        <v>43200</v>
+        <v>16200</v>
       </c>
       <c r="G27" s="3">
-        <v>110500</v>
+        <v>41600</v>
       </c>
       <c r="H27" s="3">
-        <v>103700</v>
+        <v>106300</v>
       </c>
       <c r="I27" s="3">
-        <v>106100</v>
+        <v>99700</v>
       </c>
       <c r="J27" s="3">
+        <v>102000</v>
+      </c>
+      <c r="K27" s="3">
         <v>175600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>151600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>37000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>111600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>138700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>204000</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1625,8 +1682,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1639,41 +1699,44 @@
       <c r="F29" s="3">
         <v>0</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H29" s="3">
-        <v>-214700</v>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I29" s="3">
-        <v>0</v>
+        <v>-206500</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>263500</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-73000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>59900</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>60700</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-37700</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1719,8 +1782,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1766,102 +1832,111 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>-94700</v>
       </c>
       <c r="E32" s="3">
-        <v>-4400</v>
+        <v>-81200</v>
       </c>
       <c r="F32" s="3">
-        <v>-58200</v>
+        <v>-4200</v>
       </c>
       <c r="G32" s="3">
-        <v>-212500</v>
+        <v>-56000</v>
       </c>
       <c r="H32" s="3">
-        <v>73300</v>
+        <v>-204400</v>
       </c>
       <c r="I32" s="3">
-        <v>-35600</v>
+        <v>70500</v>
       </c>
       <c r="J32" s="3">
+        <v>-34200</v>
+      </c>
+      <c r="K32" s="3">
         <v>-141100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-151400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>32600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-58500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-91300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-81900</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>3</v>
+      <c r="D33" s="3">
+        <v>28400</v>
       </c>
       <c r="E33" s="3">
-        <v>16800</v>
+        <v>195500</v>
       </c>
       <c r="F33" s="3">
-        <v>43200</v>
+        <v>16200</v>
       </c>
       <c r="G33" s="3">
-        <v>110500</v>
+        <v>41600</v>
       </c>
       <c r="H33" s="3">
-        <v>-111000</v>
+        <v>106300</v>
       </c>
       <c r="I33" s="3">
-        <v>106100</v>
+        <v>-106800</v>
       </c>
       <c r="J33" s="3">
+        <v>102000</v>
+      </c>
+      <c r="K33" s="3">
         <v>175600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>415100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-36100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>171500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>199400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>166300</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1907,107 +1982,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>3</v>
+      <c r="D35" s="3">
+        <v>28400</v>
       </c>
       <c r="E35" s="3">
-        <v>16800</v>
+        <v>195500</v>
       </c>
       <c r="F35" s="3">
-        <v>43200</v>
+        <v>16200</v>
       </c>
       <c r="G35" s="3">
-        <v>110500</v>
+        <v>41600</v>
       </c>
       <c r="H35" s="3">
-        <v>-111000</v>
+        <v>106300</v>
       </c>
       <c r="I35" s="3">
-        <v>106100</v>
+        <v>-106800</v>
       </c>
       <c r="J35" s="3">
+        <v>102000</v>
+      </c>
+      <c r="K35" s="3">
         <v>175600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>415100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-36100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>171500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>199400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>166300</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2025,8 +2109,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2044,102 +2129,109 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>3</v>
+      <c r="D41" s="3">
+        <v>4642100</v>
       </c>
       <c r="E41" s="3">
-        <v>4779400</v>
+        <v>4649500</v>
       </c>
       <c r="F41" s="3">
-        <v>4990900</v>
+        <v>4595600</v>
       </c>
       <c r="G41" s="3">
-        <v>5025200</v>
+        <v>4798900</v>
       </c>
       <c r="H41" s="3">
-        <v>4428500</v>
+        <v>4832000</v>
       </c>
       <c r="I41" s="3">
-        <v>4683600</v>
+        <v>4258200</v>
       </c>
       <c r="J41" s="3">
+        <v>4503500</v>
+      </c>
+      <c r="K41" s="3">
         <v>5574700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3937700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8794300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7896300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7478900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7377700</v>
       </c>
-      <c r="P41" s="3">
-        <v>0</v>
-      </c>
       <c r="Q41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>12980600</v>
+        <v>13000900</v>
       </c>
       <c r="E42" s="3">
-        <v>12137300</v>
+        <v>12481400</v>
       </c>
       <c r="F42" s="3">
-        <v>12000300</v>
+        <v>11670500</v>
       </c>
       <c r="G42" s="3">
-        <v>11853300</v>
+        <v>11538800</v>
       </c>
       <c r="H42" s="3">
-        <v>11839600</v>
+        <v>11397400</v>
       </c>
       <c r="I42" s="3">
-        <v>11466600</v>
+        <v>11384200</v>
       </c>
       <c r="J42" s="3">
+        <v>11025600</v>
+      </c>
+      <c r="K42" s="3">
         <v>11083300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>9948200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>13366900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>11815200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>11196400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>10964900</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2185,8 +2277,11 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2232,8 +2327,11 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2279,8 +2377,11 @@
       <c r="Q45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2326,149 +2427,161 @@
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>335600</v>
+        <v>281000</v>
       </c>
       <c r="E47" s="3">
-        <v>325200</v>
+        <v>322700</v>
       </c>
       <c r="F47" s="3">
-        <v>315000</v>
+        <v>312700</v>
       </c>
       <c r="G47" s="3">
-        <v>309800</v>
+        <v>302900</v>
       </c>
       <c r="H47" s="3">
-        <v>370100</v>
+        <v>297800</v>
       </c>
       <c r="I47" s="3">
-        <v>1428400</v>
+        <v>355800</v>
       </c>
       <c r="J47" s="3">
+        <v>1373400</v>
+      </c>
+      <c r="K47" s="3">
         <v>1269300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1045700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>281500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>236900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>222000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>203600</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1818900</v>
+        <v>1773600</v>
       </c>
       <c r="E48" s="3">
-        <v>1830100</v>
+        <v>1749000</v>
       </c>
       <c r="F48" s="3">
-        <v>1849500</v>
+        <v>1759700</v>
       </c>
       <c r="G48" s="3">
-        <v>1884400</v>
+        <v>1778400</v>
       </c>
       <c r="H48" s="3">
-        <v>1881200</v>
+        <v>1811900</v>
       </c>
       <c r="I48" s="3">
-        <v>1852700</v>
+        <v>1808900</v>
       </c>
       <c r="J48" s="3">
+        <v>1781500</v>
+      </c>
+      <c r="K48" s="3">
         <v>1831400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1680800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2184100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1943400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1863500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1891300</v>
       </c>
-      <c r="P48" s="3">
-        <v>0</v>
-      </c>
       <c r="Q48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>4716900</v>
+        <v>4555600</v>
       </c>
       <c r="E49" s="3">
-        <v>4691600</v>
+        <v>4535500</v>
       </c>
       <c r="F49" s="3">
-        <v>4667000</v>
+        <v>4511100</v>
       </c>
       <c r="G49" s="3">
-        <v>4641300</v>
+        <v>4487500</v>
       </c>
       <c r="H49" s="3">
-        <v>4558100</v>
+        <v>4462800</v>
       </c>
       <c r="I49" s="3">
-        <v>4365200</v>
+        <v>4382800</v>
       </c>
       <c r="J49" s="3">
+        <v>4197300</v>
+      </c>
+      <c r="K49" s="3">
         <v>4169400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3659200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5153000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4526400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4199400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4064600</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
-      </c>
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2514,8 +2627,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2561,55 +2677,61 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>359300</v>
+        <v>25800</v>
       </c>
       <c r="E52" s="3">
-        <v>24500</v>
+        <v>345500</v>
       </c>
       <c r="F52" s="3">
-        <v>30600</v>
+        <v>23600</v>
       </c>
       <c r="G52" s="3">
-        <v>26000</v>
+        <v>29400</v>
       </c>
       <c r="H52" s="3">
-        <v>505500</v>
+        <v>25000</v>
       </c>
       <c r="I52" s="3">
-        <v>35800</v>
+        <v>486000</v>
       </c>
       <c r="J52" s="3">
+        <v>34400</v>
+      </c>
+      <c r="K52" s="3">
         <v>37700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>35300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>473700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>31700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>26300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>52600</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
       <c r="Q52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2655,55 +2777,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>3</v>
+      <c r="D54" s="3">
+        <v>76723000</v>
       </c>
       <c r="E54" s="3">
-        <v>77670400</v>
+        <v>75295400</v>
       </c>
       <c r="F54" s="3">
-        <v>77496000</v>
+        <v>74683100</v>
       </c>
       <c r="G54" s="3">
-        <v>77708300</v>
+        <v>74515400</v>
       </c>
       <c r="H54" s="3">
-        <v>76853700</v>
+        <v>74719500</v>
       </c>
       <c r="I54" s="3">
-        <v>74333000</v>
+        <v>73897800</v>
       </c>
       <c r="J54" s="3">
+        <v>71474100</v>
+      </c>
+      <c r="K54" s="3">
         <v>71788900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>62669800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>88056900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>77375100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>72292900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>70751400</v>
       </c>
-      <c r="P54" s="3">
-        <v>0</v>
-      </c>
       <c r="Q54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2721,8 +2849,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2740,55 +2869,59 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>3</v>
+      <c r="D57" s="3">
+        <v>809700</v>
       </c>
       <c r="E57" s="3">
-        <v>713800</v>
+        <v>868500</v>
       </c>
       <c r="F57" s="3">
-        <v>711600</v>
+        <v>686300</v>
       </c>
       <c r="G57" s="3">
-        <v>717500</v>
+        <v>684200</v>
       </c>
       <c r="H57" s="3">
-        <v>729000</v>
+        <v>689900</v>
       </c>
       <c r="I57" s="3">
-        <v>665700</v>
+        <v>700900</v>
       </c>
       <c r="J57" s="3">
+        <v>640100</v>
+      </c>
+      <c r="K57" s="3">
         <v>663800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>569900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>774800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>641300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>596400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>572900</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
       <c r="Q57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2834,55 +2967,61 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>69800</v>
+        <v>1929600</v>
       </c>
       <c r="E59" s="3">
-        <v>1887700</v>
+        <v>314200</v>
       </c>
       <c r="F59" s="3">
-        <v>1982800</v>
+        <v>1815100</v>
       </c>
       <c r="G59" s="3">
-        <v>2128200</v>
+        <v>1906600</v>
       </c>
       <c r="H59" s="3">
-        <v>243000</v>
+        <v>2046400</v>
       </c>
       <c r="I59" s="3">
-        <v>1520600</v>
+        <v>233700</v>
       </c>
       <c r="J59" s="3">
+        <v>1462100</v>
+      </c>
+      <c r="K59" s="3">
         <v>1427000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1298500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>387400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1382400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1246800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1332200</v>
       </c>
-      <c r="P59" s="3">
-        <v>0</v>
-      </c>
       <c r="Q59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2928,102 +3067,111 @@
       <c r="Q60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>13119400</v>
+        <v>12215900</v>
       </c>
       <c r="E61" s="3">
-        <v>13820800</v>
+        <v>12614900</v>
       </c>
       <c r="F61" s="3">
-        <v>13900700</v>
+        <v>13289200</v>
       </c>
       <c r="G61" s="3">
-        <v>15922100</v>
+        <v>13366000</v>
       </c>
       <c r="H61" s="3">
-        <v>16387500</v>
+        <v>15309700</v>
       </c>
       <c r="I61" s="3">
-        <v>15353900</v>
+        <v>15757200</v>
       </c>
       <c r="J61" s="3">
+        <v>14763300</v>
+      </c>
+      <c r="K61" s="3">
         <v>15120000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>12389300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>15026400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>12193300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>11352000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>11073300</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1959800</v>
+        <v>391900</v>
       </c>
       <c r="E62" s="3">
-        <v>383200</v>
+        <v>1788100</v>
       </c>
       <c r="F62" s="3">
-        <v>394200</v>
+        <v>368500</v>
       </c>
       <c r="G62" s="3">
-        <v>417100</v>
+        <v>379000</v>
       </c>
       <c r="H62" s="3">
-        <v>1756100</v>
+        <v>401000</v>
       </c>
       <c r="I62" s="3">
-        <v>406600</v>
+        <v>1688600</v>
       </c>
       <c r="J62" s="3">
+        <v>390900</v>
+      </c>
+      <c r="K62" s="3">
         <v>404600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>393900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1462300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>348700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>332700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>339500</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3069,8 +3217,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3116,8 +3267,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3163,55 +3317,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>73943700</v>
+        <v>72610000</v>
       </c>
       <c r="E66" s="3">
-        <v>73411200</v>
+        <v>71099700</v>
       </c>
       <c r="F66" s="3">
-        <v>73215000</v>
+        <v>70587700</v>
       </c>
       <c r="G66" s="3">
-        <v>73502600</v>
+        <v>70399000</v>
       </c>
       <c r="H66" s="3">
-        <v>72572300</v>
+        <v>70675600</v>
       </c>
       <c r="I66" s="3">
-        <v>69973700</v>
+        <v>69781100</v>
       </c>
       <c r="J66" s="3">
+        <v>67282400</v>
+      </c>
+      <c r="K66" s="3">
         <v>67519700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>58774500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>82533700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>72460600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>67787200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>66472500</v>
       </c>
-      <c r="P66" s="3">
-        <v>0</v>
-      </c>
       <c r="Q66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3229,8 +3389,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3276,8 +3437,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3323,8 +3487,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3370,8 +3537,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3417,55 +3587,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2010300</v>
+        <v>1819700</v>
       </c>
       <c r="E72" s="3">
-        <v>1986800</v>
+        <v>1932900</v>
       </c>
       <c r="F72" s="3">
-        <v>1972000</v>
+        <v>1910400</v>
       </c>
       <c r="G72" s="3">
-        <v>1931400</v>
+        <v>1896100</v>
       </c>
       <c r="H72" s="3">
-        <v>2084800</v>
+        <v>1857100</v>
       </c>
       <c r="I72" s="3">
-        <v>2171200</v>
+        <v>2004600</v>
       </c>
       <c r="J72" s="3">
+        <v>2087700</v>
+      </c>
+      <c r="K72" s="3">
         <v>2065500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2032800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3212000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2777700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2486200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2287600</v>
       </c>
-      <c r="P72" s="3">
-        <v>0</v>
-      </c>
       <c r="Q72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3511,8 +3687,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3558,8 +3737,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3605,55 +3787,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4363500</v>
+        <v>4113000</v>
       </c>
       <c r="E76" s="3">
-        <v>4259200</v>
+        <v>4195700</v>
       </c>
       <c r="F76" s="3">
-        <v>4281000</v>
+        <v>4095400</v>
       </c>
       <c r="G76" s="3">
-        <v>4205700</v>
+        <v>4116400</v>
       </c>
       <c r="H76" s="3">
-        <v>4281400</v>
+        <v>4043900</v>
       </c>
       <c r="I76" s="3">
-        <v>4359300</v>
+        <v>4116700</v>
       </c>
       <c r="J76" s="3">
+        <v>4191600</v>
+      </c>
+      <c r="K76" s="3">
         <v>4269200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3895300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5523300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4914500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4505700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4279000</v>
       </c>
-      <c r="P76" s="3">
-        <v>0</v>
-      </c>
       <c r="Q76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3699,107 +3887,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>3</v>
+      <c r="D81" s="3">
+        <v>28400</v>
       </c>
       <c r="E81" s="3">
-        <v>16800</v>
+        <v>195500</v>
       </c>
       <c r="F81" s="3">
-        <v>43200</v>
+        <v>16200</v>
       </c>
       <c r="G81" s="3">
-        <v>110500</v>
+        <v>41600</v>
       </c>
       <c r="H81" s="3">
-        <v>-111000</v>
+        <v>106300</v>
       </c>
       <c r="I81" s="3">
-        <v>106100</v>
+        <v>-106800</v>
       </c>
       <c r="J81" s="3">
+        <v>102000</v>
+      </c>
+      <c r="K81" s="3">
         <v>175600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>415100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-36100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>171500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>199400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>166300</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3817,55 +4014,59 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>75500</v>
       </c>
       <c r="E83" s="3">
+        <v>75300</v>
+      </c>
+      <c r="F83" s="3">
+        <v>72000</v>
+      </c>
+      <c r="G83" s="3">
+        <v>70600</v>
+      </c>
+      <c r="H83" s="3">
+        <v>69900</v>
+      </c>
+      <c r="I83" s="3">
+        <v>71400</v>
+      </c>
+      <c r="J83" s="3">
+        <v>67700</v>
+      </c>
+      <c r="K83" s="3">
+        <v>70400</v>
+      </c>
+      <c r="L83" s="3">
+        <v>63200</v>
+      </c>
+      <c r="M83" s="3">
+        <v>89100</v>
+      </c>
+      <c r="N83" s="3">
+        <v>80700</v>
+      </c>
+      <c r="O83" s="3">
+        <v>73900</v>
+      </c>
+      <c r="P83" s="3">
         <v>74800</v>
       </c>
-      <c r="F83" s="3">
-        <v>73500</v>
-      </c>
-      <c r="G83" s="3">
-        <v>72700</v>
-      </c>
-      <c r="H83" s="3">
-        <v>74300</v>
-      </c>
-      <c r="I83" s="3">
-        <v>70400</v>
-      </c>
-      <c r="J83" s="3">
-        <v>70400</v>
-      </c>
-      <c r="K83" s="3">
-        <v>63200</v>
-      </c>
-      <c r="L83" s="3">
-        <v>89100</v>
-      </c>
-      <c r="M83" s="3">
-        <v>80700</v>
-      </c>
-      <c r="N83" s="3">
-        <v>73900</v>
-      </c>
-      <c r="O83" s="3">
-        <v>74800</v>
-      </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3911,8 +4112,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3958,8 +4162,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4005,8 +4212,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4052,8 +4262,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4099,55 +4312,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3">
+        <v>694300</v>
       </c>
       <c r="E89" s="3">
-        <v>316600</v>
+        <v>706500</v>
       </c>
       <c r="F89" s="3">
-        <v>322400</v>
+        <v>304400</v>
       </c>
       <c r="G89" s="3">
-        <v>187800</v>
+        <v>310000</v>
       </c>
       <c r="H89" s="3">
-        <v>-1081700</v>
+        <v>180600</v>
       </c>
       <c r="I89" s="3">
-        <v>-346300</v>
+        <v>-1040100</v>
       </c>
       <c r="J89" s="3">
+        <v>-333000</v>
+      </c>
+      <c r="K89" s="3">
         <v>1538000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-489300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>495500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-21700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>505500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>321100</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
       <c r="Q89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4165,55 +4384,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-147628000</v>
+        <v>-284289000</v>
       </c>
       <c r="E91" s="3">
+        <v>-441443000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-394006000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-257519000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-205678000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-482508000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-281054000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-238582000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-143769000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-489803000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-299606000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-24200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-16300</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4259,8 +4482,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4306,55 +4532,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>-442500</v>
       </c>
       <c r="E94" s="3">
-        <v>-240700</v>
+        <v>-18700</v>
       </c>
       <c r="F94" s="3">
-        <v>59600</v>
+        <v>-231500</v>
       </c>
       <c r="G94" s="3">
-        <v>679100</v>
+        <v>57300</v>
       </c>
       <c r="H94" s="3">
-        <v>717400</v>
+        <v>653000</v>
       </c>
       <c r="I94" s="3">
-        <v>359600</v>
+        <v>689800</v>
       </c>
       <c r="J94" s="3">
+        <v>345800</v>
+      </c>
+      <c r="K94" s="3">
         <v>47900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4161400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-522800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>67100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-178900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-814100</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4372,55 +4604,59 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-66300</v>
+        <v>-63800</v>
       </c>
       <c r="E96" s="3">
-        <v>-66300</v>
+        <v>-63800</v>
       </c>
       <c r="F96" s="3">
-        <v>-66300</v>
+        <v>-63800</v>
       </c>
       <c r="G96" s="3">
+        <v>-63800</v>
+      </c>
+      <c r="H96" s="3">
         <v>-400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-500</v>
       </c>
-      <c r="I96" s="3">
-        <v>-700</v>
-      </c>
       <c r="J96" s="3">
+        <v>-600</v>
+      </c>
+      <c r="K96" s="3">
         <v>-28600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-72000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-72100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-66000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-62900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-69500</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4466,8 +4702,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4513,8 +4752,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4560,145 +4802,157 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-269100</v>
+        <v>-293000</v>
       </c>
       <c r="E100" s="3">
-        <v>-252100</v>
+        <v>-258800</v>
       </c>
       <c r="F100" s="3">
-        <v>-227900</v>
+        <v>-242400</v>
       </c>
       <c r="G100" s="3">
-        <v>-170500</v>
+        <v>-219100</v>
       </c>
       <c r="H100" s="3">
-        <v>-620900</v>
+        <v>-163900</v>
       </c>
       <c r="I100" s="3">
-        <v>-1234200</v>
+        <v>-597000</v>
       </c>
       <c r="J100" s="3">
+        <v>-1186700</v>
+      </c>
+      <c r="K100" s="3">
         <v>-276100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-89700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-18500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-57600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-229100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>17700</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-390100</v>
+        <v>33800</v>
       </c>
       <c r="E101" s="3">
-        <v>-35200</v>
+        <v>-375100</v>
       </c>
       <c r="F101" s="3">
-        <v>-188500</v>
+        <v>-33800</v>
       </c>
       <c r="G101" s="3">
-        <v>-99800</v>
+        <v>-181200</v>
       </c>
       <c r="H101" s="3">
-        <v>730100</v>
+        <v>-95900</v>
       </c>
       <c r="I101" s="3">
-        <v>329800</v>
+        <v>702000</v>
       </c>
       <c r="J101" s="3">
+        <v>317100</v>
+      </c>
+      <c r="K101" s="3">
         <v>-1000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-116100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>226000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>73500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>3600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>707700</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>56100</v>
+        <v>-7400</v>
       </c>
       <c r="E102" s="3">
-        <v>-211500</v>
+        <v>53900</v>
       </c>
       <c r="F102" s="3">
-        <v>-34400</v>
+        <v>-203300</v>
       </c>
       <c r="G102" s="3">
-        <v>596700</v>
+        <v>-33000</v>
       </c>
       <c r="H102" s="3">
-        <v>-255100</v>
+        <v>573700</v>
       </c>
       <c r="I102" s="3">
-        <v>-891100</v>
+        <v>-245300</v>
       </c>
       <c r="J102" s="3">
+        <v>-856800</v>
+      </c>
+      <c r="K102" s="3">
         <v>1308800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4856600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>180100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>61300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>101100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>232400</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
       <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AVAL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AVAL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="92">
   <si>
     <t>AVAL</t>
   </si>
@@ -656,130 +656,136 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>1809000</v>
+        <v>1737300</v>
       </c>
       <c r="E8" s="3">
-        <v>1855500</v>
+        <v>1736700</v>
       </c>
       <c r="F8" s="3">
-        <v>1833700</v>
+        <v>1781300</v>
       </c>
       <c r="G8" s="3">
-        <v>1788600</v>
+        <v>1760300</v>
       </c>
       <c r="H8" s="3">
-        <v>1752100</v>
+        <v>1717100</v>
       </c>
       <c r="I8" s="3">
-        <v>1535900</v>
+        <v>1682000</v>
       </c>
       <c r="J8" s="3">
+        <v>1474500</v>
+      </c>
+      <c r="K8" s="3">
         <v>1303200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1114500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>902300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>578700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>707300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>660300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>653500</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -828,8 +834,11 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -878,8 +887,11 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -898,8 +910,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -948,8 +961,11 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -998,8 +1014,11 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1042,64 +1061,70 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-75500</v>
+        <v>-74500</v>
       </c>
       <c r="E15" s="3">
-        <v>-75300</v>
+        <v>-72500</v>
       </c>
       <c r="F15" s="3">
-        <v>-72000</v>
+        <v>-72300</v>
       </c>
       <c r="G15" s="3">
-        <v>-70600</v>
+        <v>-69100</v>
       </c>
       <c r="H15" s="3">
-        <v>-69900</v>
+        <v>-67800</v>
       </c>
       <c r="I15" s="3">
-        <v>-71400</v>
+        <v>-67100</v>
       </c>
       <c r="J15" s="3">
+        <v>-68600</v>
+      </c>
+      <c r="K15" s="3">
         <v>-67700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-70400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-63200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-62600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-57200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-52400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-52900</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1115,108 +1140,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1729000</v>
+        <v>1512900</v>
       </c>
       <c r="E17" s="3">
-        <v>1781700</v>
+        <v>1659800</v>
       </c>
       <c r="F17" s="3">
-        <v>1718600</v>
+        <v>1710500</v>
       </c>
       <c r="G17" s="3">
-        <v>1641800</v>
+        <v>1649900</v>
       </c>
       <c r="H17" s="3">
-        <v>1561500</v>
+        <v>1576200</v>
       </c>
       <c r="I17" s="3">
-        <v>1257900</v>
+        <v>1499000</v>
       </c>
       <c r="J17" s="3">
+        <v>1207500</v>
+      </c>
+      <c r="K17" s="3">
         <v>968100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>748600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>569900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>251700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>364100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>387300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>404100</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>80100</v>
+        <v>224400</v>
       </c>
       <c r="E18" s="3">
-        <v>73700</v>
+        <v>76900</v>
       </c>
       <c r="F18" s="3">
-        <v>115000</v>
+        <v>70800</v>
       </c>
       <c r="G18" s="3">
-        <v>146800</v>
+        <v>110400</v>
       </c>
       <c r="H18" s="3">
-        <v>190600</v>
+        <v>140900</v>
       </c>
       <c r="I18" s="3">
-        <v>278000</v>
+        <v>183000</v>
       </c>
       <c r="J18" s="3">
+        <v>266900</v>
+      </c>
+      <c r="K18" s="3">
         <v>335100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>366000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>332400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>326900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>343200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>273000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>249400</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1235,108 +1267,115 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>94700</v>
+        <v>-41000</v>
       </c>
       <c r="E20" s="3">
-        <v>81200</v>
+        <v>90900</v>
       </c>
       <c r="F20" s="3">
-        <v>4200</v>
+        <v>77900</v>
       </c>
       <c r="G20" s="3">
-        <v>56000</v>
+        <v>4000</v>
       </c>
       <c r="H20" s="3">
-        <v>204400</v>
+        <v>53700</v>
       </c>
       <c r="I20" s="3">
-        <v>-70500</v>
+        <v>196200</v>
       </c>
       <c r="J20" s="3">
+        <v>-67700</v>
+      </c>
+      <c r="K20" s="3">
         <v>34200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>141100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>151400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-32600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>58500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>91300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>81900</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>250300</v>
+        <v>257900</v>
       </c>
       <c r="E21" s="3">
-        <v>230200</v>
+        <v>240200</v>
       </c>
       <c r="F21" s="3">
-        <v>191200</v>
+        <v>221000</v>
       </c>
       <c r="G21" s="3">
-        <v>273400</v>
+        <v>183500</v>
       </c>
       <c r="H21" s="3">
-        <v>464800</v>
+        <v>262500</v>
       </c>
       <c r="I21" s="3">
-        <v>279000</v>
+        <v>446300</v>
       </c>
       <c r="J21" s="3">
+        <v>267800</v>
+      </c>
+      <c r="K21" s="3">
         <v>437100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>577500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>547100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>383500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>482300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>438200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>406100</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1379,114 +1418,123 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
+      <c r="Q22" s="3">
+        <v>0</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>174700</v>
+        <v>183500</v>
       </c>
       <c r="E23" s="3">
-        <v>154900</v>
+        <v>167700</v>
       </c>
       <c r="F23" s="3">
-        <v>119200</v>
+        <v>148700</v>
       </c>
       <c r="G23" s="3">
-        <v>202800</v>
+        <v>114500</v>
       </c>
       <c r="H23" s="3">
-        <v>395000</v>
+        <v>194700</v>
       </c>
       <c r="I23" s="3">
-        <v>207600</v>
+        <v>379200</v>
       </c>
       <c r="J23" s="3">
+        <v>199300</v>
+      </c>
+      <c r="K23" s="3">
         <v>369400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>507100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>483900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>294300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>401700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>364300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>331300</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>56400</v>
+        <v>75700</v>
       </c>
       <c r="E24" s="3">
-        <v>62800</v>
+        <v>54200</v>
       </c>
       <c r="F24" s="3">
-        <v>44100</v>
+        <v>60300</v>
       </c>
       <c r="G24" s="3">
-        <v>87600</v>
+        <v>42300</v>
       </c>
       <c r="H24" s="3">
-        <v>133100</v>
+        <v>84100</v>
       </c>
       <c r="I24" s="3">
-        <v>131600</v>
+        <v>127800</v>
       </c>
       <c r="J24" s="3">
+        <v>126300</v>
+      </c>
+      <c r="K24" s="3">
         <v>137000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>146700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>151900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>91000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>222600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>92500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>103300</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1535,108 +1583,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>118300</v>
+        <v>107800</v>
       </c>
       <c r="E26" s="3">
-        <v>92100</v>
+        <v>113600</v>
       </c>
       <c r="F26" s="3">
-        <v>75200</v>
+        <v>88500</v>
       </c>
       <c r="G26" s="3">
-        <v>115100</v>
+        <v>72200</v>
       </c>
       <c r="H26" s="3">
-        <v>261800</v>
+        <v>110500</v>
       </c>
       <c r="I26" s="3">
-        <v>76000</v>
+        <v>251300</v>
       </c>
       <c r="J26" s="3">
+        <v>72900</v>
+      </c>
+      <c r="K26" s="3">
         <v>232400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>360400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>332000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>203300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>179100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>271800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>228000</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>28400</v>
+        <v>49000</v>
       </c>
       <c r="E27" s="3">
-        <v>195500</v>
+        <v>27300</v>
       </c>
       <c r="F27" s="3">
-        <v>16200</v>
+        <v>187700</v>
       </c>
       <c r="G27" s="3">
-        <v>41600</v>
+        <v>15600</v>
       </c>
       <c r="H27" s="3">
-        <v>106300</v>
+        <v>39900</v>
       </c>
       <c r="I27" s="3">
-        <v>99700</v>
+        <v>102000</v>
       </c>
       <c r="J27" s="3">
+        <v>95700</v>
+      </c>
+      <c r="K27" s="3">
         <v>102000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>175600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>151600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>37000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>111600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>138700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>204000</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1685,13 +1742,16 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
@@ -1702,41 +1762,44 @@
       <c r="G29" s="3">
         <v>0</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I29" s="3">
-        <v>-206500</v>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J29" s="3">
-        <v>0</v>
+        <v>-198200</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>263500</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-73000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>59900</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>60700</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-37700</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1785,8 +1848,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1835,108 +1901,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-94700</v>
+        <v>41000</v>
       </c>
       <c r="E32" s="3">
-        <v>-81200</v>
+        <v>-90900</v>
       </c>
       <c r="F32" s="3">
-        <v>-4200</v>
+        <v>-77900</v>
       </c>
       <c r="G32" s="3">
-        <v>-56000</v>
+        <v>-4000</v>
       </c>
       <c r="H32" s="3">
-        <v>-204400</v>
+        <v>-53700</v>
       </c>
       <c r="I32" s="3">
-        <v>70500</v>
+        <v>-196200</v>
       </c>
       <c r="J32" s="3">
+        <v>67700</v>
+      </c>
+      <c r="K32" s="3">
         <v>-34200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-141100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-151400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>32600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-58500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-91300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-81900</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>28400</v>
+        <v>49000</v>
       </c>
       <c r="E33" s="3">
-        <v>195500</v>
+        <v>27300</v>
       </c>
       <c r="F33" s="3">
-        <v>16200</v>
+        <v>187700</v>
       </c>
       <c r="G33" s="3">
-        <v>41600</v>
+        <v>15600</v>
       </c>
       <c r="H33" s="3">
-        <v>106300</v>
+        <v>39900</v>
       </c>
       <c r="I33" s="3">
-        <v>-106800</v>
+        <v>102000</v>
       </c>
       <c r="J33" s="3">
+        <v>-102500</v>
+      </c>
+      <c r="K33" s="3">
         <v>102000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>175600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>415100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-36100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>171500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>199400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>166300</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1985,113 +2060,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>28400</v>
+        <v>49000</v>
       </c>
       <c r="E35" s="3">
-        <v>195500</v>
+        <v>27300</v>
       </c>
       <c r="F35" s="3">
-        <v>16200</v>
+        <v>187700</v>
       </c>
       <c r="G35" s="3">
-        <v>41600</v>
+        <v>15600</v>
       </c>
       <c r="H35" s="3">
-        <v>106300</v>
+        <v>39900</v>
       </c>
       <c r="I35" s="3">
-        <v>-106800</v>
+        <v>102000</v>
       </c>
       <c r="J35" s="3">
+        <v>-102500</v>
+      </c>
+      <c r="K35" s="3">
         <v>102000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>175600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>415100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-36100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>171500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>199400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>166300</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2110,8 +2194,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2130,108 +2215,115 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>4642100</v>
+        <v>4631100</v>
       </c>
       <c r="E41" s="3">
-        <v>4649500</v>
+        <v>4456400</v>
       </c>
       <c r="F41" s="3">
-        <v>4595600</v>
+        <v>4463500</v>
       </c>
       <c r="G41" s="3">
-        <v>4798900</v>
+        <v>4411700</v>
       </c>
       <c r="H41" s="3">
-        <v>4832000</v>
+        <v>4607000</v>
       </c>
       <c r="I41" s="3">
-        <v>4258200</v>
+        <v>4638700</v>
       </c>
       <c r="J41" s="3">
+        <v>4087900</v>
+      </c>
+      <c r="K41" s="3">
         <v>4503500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5574700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3937700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8794300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7896300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7478900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7377700</v>
       </c>
-      <c r="Q41" s="3">
-        <v>0</v>
-      </c>
       <c r="R41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>13000900</v>
+        <v>12924200</v>
       </c>
       <c r="E42" s="3">
-        <v>12481400</v>
+        <v>12480800</v>
       </c>
       <c r="F42" s="3">
-        <v>11670500</v>
+        <v>11982100</v>
       </c>
       <c r="G42" s="3">
-        <v>11538800</v>
+        <v>11203700</v>
       </c>
       <c r="H42" s="3">
-        <v>11397400</v>
+        <v>11077200</v>
       </c>
       <c r="I42" s="3">
-        <v>11384200</v>
+        <v>10941500</v>
       </c>
       <c r="J42" s="3">
+        <v>10928800</v>
+      </c>
+      <c r="K42" s="3">
         <v>11025600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>11083300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>9948200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>13366900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>11815200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>11196400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>10964900</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2280,8 +2372,11 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2330,8 +2425,11 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2380,8 +2478,11 @@
       <c r="R45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2430,158 +2531,170 @@
       <c r="R46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>281000</v>
+        <v>298200</v>
       </c>
       <c r="E47" s="3">
-        <v>322700</v>
+        <v>269700</v>
       </c>
       <c r="F47" s="3">
-        <v>312700</v>
+        <v>309800</v>
       </c>
       <c r="G47" s="3">
-        <v>302900</v>
+        <v>300100</v>
       </c>
       <c r="H47" s="3">
-        <v>297800</v>
+        <v>290700</v>
       </c>
       <c r="I47" s="3">
-        <v>355800</v>
+        <v>285900</v>
       </c>
       <c r="J47" s="3">
+        <v>341600</v>
+      </c>
+      <c r="K47" s="3">
         <v>1373400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1269300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1045700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>281500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>236900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>222000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>203600</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1773600</v>
+        <v>1727600</v>
       </c>
       <c r="E48" s="3">
-        <v>1749000</v>
+        <v>1702700</v>
       </c>
       <c r="F48" s="3">
-        <v>1759700</v>
+        <v>1679000</v>
       </c>
       <c r="G48" s="3">
-        <v>1778400</v>
+        <v>1689300</v>
       </c>
       <c r="H48" s="3">
-        <v>1811900</v>
+        <v>1707300</v>
       </c>
       <c r="I48" s="3">
-        <v>1808900</v>
+        <v>1739500</v>
       </c>
       <c r="J48" s="3">
+        <v>1736500</v>
+      </c>
+      <c r="K48" s="3">
         <v>1781500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1831400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1680800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2184100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1943400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1863500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1891300</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
-      </c>
       <c r="R48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>4555600</v>
+        <v>4470200</v>
       </c>
       <c r="E49" s="3">
-        <v>4535500</v>
+        <v>4373400</v>
       </c>
       <c r="F49" s="3">
-        <v>4511100</v>
+        <v>4354100</v>
       </c>
       <c r="G49" s="3">
-        <v>4487500</v>
+        <v>4330700</v>
       </c>
       <c r="H49" s="3">
-        <v>4462800</v>
+        <v>4308000</v>
       </c>
       <c r="I49" s="3">
-        <v>4382800</v>
+        <v>4284300</v>
       </c>
       <c r="J49" s="3">
+        <v>4207500</v>
+      </c>
+      <c r="K49" s="3">
         <v>4197300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4169400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3659200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5153000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4526400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4199400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4064600</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
-      </c>
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2630,8 +2743,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2680,58 +2796,64 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>25800</v>
+        <v>22200</v>
       </c>
       <c r="E52" s="3">
-        <v>345500</v>
+        <v>24700</v>
       </c>
       <c r="F52" s="3">
-        <v>23600</v>
+        <v>331700</v>
       </c>
       <c r="G52" s="3">
-        <v>29400</v>
+        <v>22600</v>
       </c>
       <c r="H52" s="3">
-        <v>25000</v>
+        <v>28200</v>
       </c>
       <c r="I52" s="3">
-        <v>486000</v>
+        <v>24000</v>
       </c>
       <c r="J52" s="3">
+        <v>466600</v>
+      </c>
+      <c r="K52" s="3">
         <v>34400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>37700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>35300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>473700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>31700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>26300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>52600</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
       <c r="R52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2780,58 +2902,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>76723000</v>
+        <v>75987700</v>
       </c>
       <c r="E54" s="3">
-        <v>75295400</v>
+        <v>73654100</v>
       </c>
       <c r="F54" s="3">
-        <v>74683100</v>
+        <v>72283600</v>
       </c>
       <c r="G54" s="3">
-        <v>74515400</v>
+        <v>71695800</v>
       </c>
       <c r="H54" s="3">
-        <v>74719500</v>
+        <v>71534800</v>
       </c>
       <c r="I54" s="3">
-        <v>73897800</v>
+        <v>71730800</v>
       </c>
       <c r="J54" s="3">
+        <v>70941900</v>
+      </c>
+      <c r="K54" s="3">
         <v>71474100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>71788900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>62669800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>88056900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>77375100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>72292900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>70751400</v>
       </c>
-      <c r="Q54" s="3">
-        <v>0</v>
-      </c>
       <c r="R54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2850,8 +2978,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2870,58 +2999,62 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>809700</v>
+        <v>734600</v>
       </c>
       <c r="E57" s="3">
-        <v>868500</v>
+        <v>777300</v>
       </c>
       <c r="F57" s="3">
-        <v>686300</v>
+        <v>833800</v>
       </c>
       <c r="G57" s="3">
-        <v>684200</v>
+        <v>658900</v>
       </c>
       <c r="H57" s="3">
-        <v>689900</v>
+        <v>656900</v>
       </c>
       <c r="I57" s="3">
-        <v>700900</v>
+        <v>662300</v>
       </c>
       <c r="J57" s="3">
+        <v>672900</v>
+      </c>
+      <c r="K57" s="3">
         <v>640100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>663800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>569900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>774800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>641300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>596400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>572900</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2970,58 +3103,64 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1929600</v>
+        <v>1754600</v>
       </c>
       <c r="E59" s="3">
-        <v>314200</v>
+        <v>1852400</v>
       </c>
       <c r="F59" s="3">
-        <v>1815100</v>
+        <v>301600</v>
       </c>
       <c r="G59" s="3">
-        <v>1906600</v>
+        <v>1742500</v>
       </c>
       <c r="H59" s="3">
-        <v>2046400</v>
+        <v>1830300</v>
       </c>
       <c r="I59" s="3">
-        <v>233700</v>
+        <v>1964500</v>
       </c>
       <c r="J59" s="3">
+        <v>224300</v>
+      </c>
+      <c r="K59" s="3">
         <v>1462100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1427000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1298500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>387400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1382400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1246800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1332200</v>
       </c>
-      <c r="Q59" s="3">
-        <v>0</v>
-      </c>
       <c r="R59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3070,108 +3209,117 @@
       <c r="R60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>12215900</v>
+        <v>12024500</v>
       </c>
       <c r="E61" s="3">
-        <v>12614900</v>
+        <v>11727300</v>
       </c>
       <c r="F61" s="3">
-        <v>13289200</v>
+        <v>12110300</v>
       </c>
       <c r="G61" s="3">
-        <v>13366000</v>
+        <v>12757700</v>
       </c>
       <c r="H61" s="3">
-        <v>15309700</v>
+        <v>12831400</v>
       </c>
       <c r="I61" s="3">
-        <v>15757200</v>
+        <v>14697300</v>
       </c>
       <c r="J61" s="3">
+        <v>15126900</v>
+      </c>
+      <c r="K61" s="3">
         <v>14763300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>15120000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>12389300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>15026400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>12193300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>11352000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>11073300</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>391900</v>
+        <v>366700</v>
       </c>
       <c r="E62" s="3">
-        <v>1788100</v>
+        <v>376200</v>
       </c>
       <c r="F62" s="3">
-        <v>368500</v>
+        <v>1716600</v>
       </c>
       <c r="G62" s="3">
-        <v>379000</v>
+        <v>353700</v>
       </c>
       <c r="H62" s="3">
-        <v>401000</v>
+        <v>363800</v>
       </c>
       <c r="I62" s="3">
-        <v>1688600</v>
+        <v>385000</v>
       </c>
       <c r="J62" s="3">
+        <v>1621000</v>
+      </c>
+      <c r="K62" s="3">
         <v>390900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>404600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>393900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1462300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>348700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>332700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>339500</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3220,8 +3368,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3270,8 +3421,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3320,58 +3474,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>72610000</v>
+        <v>71975000</v>
       </c>
       <c r="E66" s="3">
-        <v>71099700</v>
+        <v>69705600</v>
       </c>
       <c r="F66" s="3">
-        <v>70587700</v>
+        <v>68255700</v>
       </c>
       <c r="G66" s="3">
-        <v>70399000</v>
+        <v>67764200</v>
       </c>
       <c r="H66" s="3">
-        <v>70675600</v>
+        <v>67583100</v>
       </c>
       <c r="I66" s="3">
-        <v>69781100</v>
+        <v>67848600</v>
       </c>
       <c r="J66" s="3">
+        <v>66989800</v>
+      </c>
+      <c r="K66" s="3">
         <v>67282400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>67519700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>58774500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>82533700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>72460600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>67787200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>66472500</v>
       </c>
-      <c r="Q66" s="3">
-        <v>0</v>
-      </c>
       <c r="R66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3390,8 +3550,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3440,8 +3601,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3490,8 +3654,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3540,8 +3707,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3590,58 +3760,64 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1819700</v>
+        <v>1795700</v>
       </c>
       <c r="E72" s="3">
-        <v>1932900</v>
+        <v>1746900</v>
       </c>
       <c r="F72" s="3">
-        <v>1910400</v>
+        <v>1855600</v>
       </c>
       <c r="G72" s="3">
-        <v>1896100</v>
+        <v>1834000</v>
       </c>
       <c r="H72" s="3">
-        <v>1857100</v>
+        <v>1820300</v>
       </c>
       <c r="I72" s="3">
-        <v>2004600</v>
+        <v>1782800</v>
       </c>
       <c r="J72" s="3">
+        <v>1924400</v>
+      </c>
+      <c r="K72" s="3">
         <v>2087700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2065500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2032800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3212000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2777700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2486200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2287600</v>
       </c>
-      <c r="Q72" s="3">
-        <v>0</v>
-      </c>
       <c r="R72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3690,8 +3866,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3740,8 +3919,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3790,58 +3972,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4113000</v>
+        <v>4012800</v>
       </c>
       <c r="E76" s="3">
-        <v>4195700</v>
+        <v>3948500</v>
       </c>
       <c r="F76" s="3">
-        <v>4095400</v>
+        <v>4027800</v>
       </c>
       <c r="G76" s="3">
-        <v>4116400</v>
+        <v>3931600</v>
       </c>
       <c r="H76" s="3">
-        <v>4043900</v>
+        <v>3951700</v>
       </c>
       <c r="I76" s="3">
-        <v>4116700</v>
+        <v>3882200</v>
       </c>
       <c r="J76" s="3">
+        <v>3952100</v>
+      </c>
+      <c r="K76" s="3">
         <v>4191600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4269200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3895300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5523300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4914500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4505700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4279000</v>
       </c>
-      <c r="Q76" s="3">
-        <v>0</v>
-      </c>
       <c r="R76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3890,113 +4078,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>28400</v>
+        <v>49000</v>
       </c>
       <c r="E81" s="3">
-        <v>195500</v>
+        <v>27300</v>
       </c>
       <c r="F81" s="3">
-        <v>16200</v>
+        <v>187700</v>
       </c>
       <c r="G81" s="3">
-        <v>41600</v>
+        <v>15600</v>
       </c>
       <c r="H81" s="3">
-        <v>106300</v>
+        <v>39900</v>
       </c>
       <c r="I81" s="3">
-        <v>-106800</v>
+        <v>102000</v>
       </c>
       <c r="J81" s="3">
+        <v>-102500</v>
+      </c>
+      <c r="K81" s="3">
         <v>102000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>175600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>415100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-36100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>171500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>199400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>166300</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4015,58 +4212,62 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>75500</v>
+        <v>74500</v>
       </c>
       <c r="E83" s="3">
-        <v>75300</v>
+        <v>72500</v>
       </c>
       <c r="F83" s="3">
-        <v>72000</v>
+        <v>72300</v>
       </c>
       <c r="G83" s="3">
-        <v>70600</v>
+        <v>69100</v>
       </c>
       <c r="H83" s="3">
-        <v>69900</v>
+        <v>67800</v>
       </c>
       <c r="I83" s="3">
-        <v>71400</v>
+        <v>67100</v>
       </c>
       <c r="J83" s="3">
+        <v>68600</v>
+      </c>
+      <c r="K83" s="3">
         <v>67700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>70400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>63200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>89100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>80700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>73900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>74800</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4115,8 +4316,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4165,8 +4369,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4215,8 +4422,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4265,8 +4475,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4315,58 +4528,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>694300</v>
+        <v>-201500</v>
       </c>
       <c r="E89" s="3">
-        <v>706500</v>
+        <v>666500</v>
       </c>
       <c r="F89" s="3">
-        <v>304400</v>
+        <v>678200</v>
       </c>
       <c r="G89" s="3">
-        <v>310000</v>
+        <v>292200</v>
       </c>
       <c r="H89" s="3">
-        <v>180600</v>
+        <v>297600</v>
       </c>
       <c r="I89" s="3">
-        <v>-1040100</v>
+        <v>173300</v>
       </c>
       <c r="J89" s="3">
+        <v>-998500</v>
+      </c>
+      <c r="K89" s="3">
         <v>-333000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1538000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-489300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>495500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-21700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>505500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>321100</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
       <c r="R89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4385,58 +4604,62 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-315041000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-284289000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-441443000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-394006000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-257519000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-205678000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-482508000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-281054000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-238582000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-143769000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-489803000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-299606000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-24200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-16300</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4485,8 +4708,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4535,58 +4761,64 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-442500</v>
+        <v>101100</v>
       </c>
       <c r="E94" s="3">
-        <v>-18700</v>
+        <v>-424800</v>
       </c>
       <c r="F94" s="3">
-        <v>-231500</v>
+        <v>-17900</v>
       </c>
       <c r="G94" s="3">
-        <v>57300</v>
+        <v>-222200</v>
       </c>
       <c r="H94" s="3">
-        <v>653000</v>
+        <v>55000</v>
       </c>
       <c r="I94" s="3">
-        <v>689800</v>
+        <v>626900</v>
       </c>
       <c r="J94" s="3">
+        <v>662200</v>
+      </c>
+      <c r="K94" s="3">
         <v>345800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>47900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4161400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-522800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>67100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-178900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-814100</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4605,58 +4837,62 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-63800</v>
+        <v>-33900</v>
       </c>
       <c r="E96" s="3">
-        <v>-63800</v>
+        <v>-61200</v>
       </c>
       <c r="F96" s="3">
-        <v>-63800</v>
+        <v>-61200</v>
       </c>
       <c r="G96" s="3">
-        <v>-63800</v>
+        <v>-61200</v>
       </c>
       <c r="H96" s="3">
+        <v>-61200</v>
+      </c>
+      <c r="I96" s="3">
         <v>-400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-28600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-72000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-72100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-66000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-62900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-69500</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4705,8 +4941,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4755,8 +4994,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4805,154 +5047,166 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-293000</v>
+        <v>17700</v>
       </c>
       <c r="E100" s="3">
-        <v>-258800</v>
+        <v>-281200</v>
       </c>
       <c r="F100" s="3">
-        <v>-242400</v>
+        <v>-248400</v>
       </c>
       <c r="G100" s="3">
-        <v>-219100</v>
+        <v>-232700</v>
       </c>
       <c r="H100" s="3">
-        <v>-163900</v>
+        <v>-210300</v>
       </c>
       <c r="I100" s="3">
-        <v>-597000</v>
+        <v>-157400</v>
       </c>
       <c r="J100" s="3">
+        <v>-573100</v>
+      </c>
+      <c r="K100" s="3">
         <v>-1186700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-276100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-89700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-18500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-57600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-229100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>17700</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>33800</v>
+        <v>257400</v>
       </c>
       <c r="E101" s="3">
-        <v>-375100</v>
+        <v>32500</v>
       </c>
       <c r="F101" s="3">
-        <v>-33800</v>
+        <v>-360100</v>
       </c>
       <c r="G101" s="3">
-        <v>-181200</v>
+        <v>-32500</v>
       </c>
       <c r="H101" s="3">
-        <v>-95900</v>
+        <v>-174000</v>
       </c>
       <c r="I101" s="3">
-        <v>702000</v>
+        <v>-92100</v>
       </c>
       <c r="J101" s="3">
+        <v>673900</v>
+      </c>
+      <c r="K101" s="3">
         <v>317100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-116100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>226000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>73500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>3600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>707700</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-7400</v>
+        <v>174700</v>
       </c>
       <c r="E102" s="3">
-        <v>53900</v>
+        <v>-7100</v>
       </c>
       <c r="F102" s="3">
-        <v>-203300</v>
+        <v>51700</v>
       </c>
       <c r="G102" s="3">
-        <v>-33000</v>
+        <v>-195200</v>
       </c>
       <c r="H102" s="3">
-        <v>573700</v>
+        <v>-31700</v>
       </c>
       <c r="I102" s="3">
-        <v>-245300</v>
+        <v>550800</v>
       </c>
       <c r="J102" s="3">
+        <v>-235500</v>
+      </c>
+      <c r="K102" s="3">
         <v>-856800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1308800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4856600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>180100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>61300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>101100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>232400</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AVAL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AVAL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="92">
   <si>
     <t>AVAL</t>
   </si>
@@ -656,136 +656,148 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>1737300</v>
+        <v>748900</v>
       </c>
       <c r="E8" s="3">
-        <v>1736700</v>
+        <v>690000</v>
       </c>
       <c r="F8" s="3">
-        <v>1781300</v>
+        <v>720200</v>
       </c>
       <c r="G8" s="3">
-        <v>1760300</v>
+        <v>694700</v>
       </c>
       <c r="H8" s="3">
-        <v>1717100</v>
+        <v>604100</v>
       </c>
       <c r="I8" s="3">
-        <v>1682000</v>
+        <v>701300</v>
       </c>
       <c r="J8" s="3">
+        <v>789000</v>
+      </c>
+      <c r="K8" s="3">
         <v>1474500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1303200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1114500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>902300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>578700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>707300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>660300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>653500</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -837,31 +849,34 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>748900</v>
+      </c>
+      <c r="E10" s="3">
+        <v>690000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>720200</v>
+      </c>
+      <c r="G10" s="3">
+        <v>694700</v>
+      </c>
+      <c r="H10" s="3">
+        <v>604100</v>
+      </c>
+      <c r="I10" s="3">
+        <v>701300</v>
+      </c>
+      <c r="J10" s="3">
+        <v>789000</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -890,8 +905,11 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -911,8 +929,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -964,8 +983,11 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1017,28 +1039,31 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>-2400</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>-4100</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>-2100</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>-38600</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>-3500</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -1064,67 +1089,73 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-74500</v>
+        <v>61900</v>
       </c>
       <c r="E15" s="3">
-        <v>-72500</v>
+        <v>42000</v>
       </c>
       <c r="F15" s="3">
-        <v>-72300</v>
+        <v>78300</v>
       </c>
       <c r="G15" s="3">
-        <v>-69100</v>
+        <v>61100</v>
       </c>
       <c r="H15" s="3">
-        <v>-67800</v>
+        <v>55900</v>
       </c>
       <c r="I15" s="3">
-        <v>-67100</v>
+        <v>38500</v>
       </c>
       <c r="J15" s="3">
+        <v>60400</v>
+      </c>
+      <c r="K15" s="3">
         <v>-68600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-67700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-70400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-63200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-62600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-57200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-52400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-52900</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1141,114 +1172,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1512900</v>
+        <v>465800</v>
       </c>
       <c r="E17" s="3">
-        <v>1659800</v>
+        <v>482000</v>
       </c>
       <c r="F17" s="3">
-        <v>1710500</v>
+        <v>510900</v>
       </c>
       <c r="G17" s="3">
-        <v>1649900</v>
+        <v>561000</v>
       </c>
       <c r="H17" s="3">
-        <v>1576200</v>
+        <v>461800</v>
       </c>
       <c r="I17" s="3">
-        <v>1499000</v>
+        <v>468700</v>
       </c>
       <c r="J17" s="3">
+        <v>415300</v>
+      </c>
+      <c r="K17" s="3">
         <v>1207500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>968100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>748600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>569900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>251700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>364100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>387300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>404100</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>224400</v>
+        <v>283100</v>
       </c>
       <c r="E18" s="3">
-        <v>76900</v>
+        <v>208000</v>
       </c>
       <c r="F18" s="3">
-        <v>70800</v>
+        <v>209300</v>
       </c>
       <c r="G18" s="3">
-        <v>110400</v>
+        <v>133700</v>
       </c>
       <c r="H18" s="3">
-        <v>140900</v>
+        <v>142200</v>
       </c>
       <c r="I18" s="3">
-        <v>183000</v>
+        <v>232500</v>
       </c>
       <c r="J18" s="3">
+        <v>373700</v>
+      </c>
+      <c r="K18" s="3">
         <v>266900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>335100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>366000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>332400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>326900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>343200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>273000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>249400</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1268,137 +1306,144 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-41000</v>
+        <v>28500</v>
       </c>
       <c r="E20" s="3">
-        <v>90900</v>
+        <v>27400</v>
       </c>
       <c r="F20" s="3">
-        <v>77900</v>
+        <v>30200</v>
       </c>
       <c r="G20" s="3">
-        <v>4000</v>
+        <v>12400</v>
       </c>
       <c r="H20" s="3">
-        <v>53700</v>
+        <v>27900</v>
       </c>
       <c r="I20" s="3">
-        <v>196200</v>
+        <v>31100</v>
       </c>
       <c r="J20" s="3">
+        <v>32500</v>
+      </c>
+      <c r="K20" s="3">
         <v>-67700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>34200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>141100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>151400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-32600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>58500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>91300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>81900</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>257900</v>
+        <v>316400</v>
       </c>
       <c r="E21" s="3">
-        <v>240200</v>
+        <v>222600</v>
       </c>
       <c r="F21" s="3">
-        <v>221000</v>
+        <v>257300</v>
       </c>
       <c r="G21" s="3">
-        <v>183500</v>
+        <v>182400</v>
       </c>
       <c r="H21" s="3">
-        <v>262500</v>
+        <v>170200</v>
       </c>
       <c r="I21" s="3">
-        <v>446300</v>
+        <v>239900</v>
       </c>
       <c r="J21" s="3">
+        <v>401700</v>
+      </c>
+      <c r="K21" s="3">
         <v>267800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>437100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>577500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>547100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>383500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>482300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>438200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>406100</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1421,120 +1466,129 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
+      <c r="R22" s="3">
+        <v>0</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>183500</v>
+        <v>256900</v>
       </c>
       <c r="E23" s="3">
-        <v>167700</v>
+        <v>184800</v>
       </c>
       <c r="F23" s="3">
-        <v>148700</v>
+        <v>181100</v>
       </c>
       <c r="G23" s="3">
-        <v>114500</v>
+        <v>160000</v>
       </c>
       <c r="H23" s="3">
-        <v>194700</v>
+        <v>117900</v>
       </c>
       <c r="I23" s="3">
-        <v>379200</v>
+        <v>194400</v>
       </c>
       <c r="J23" s="3">
+        <v>341300</v>
+      </c>
+      <c r="K23" s="3">
         <v>199300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>369400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>507100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>483900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>294300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>401700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>364300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>331300</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>75700</v>
+        <v>82100</v>
       </c>
       <c r="E24" s="3">
-        <v>54200</v>
+        <v>76200</v>
       </c>
       <c r="F24" s="3">
-        <v>60300</v>
+        <v>58500</v>
       </c>
       <c r="G24" s="3">
-        <v>42300</v>
+        <v>64800</v>
       </c>
       <c r="H24" s="3">
-        <v>84100</v>
+        <v>43600</v>
       </c>
       <c r="I24" s="3">
-        <v>127800</v>
+        <v>84000</v>
       </c>
       <c r="J24" s="3">
+        <v>115000</v>
+      </c>
+      <c r="K24" s="3">
         <v>126300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>137000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>146700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>151900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>91000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>222600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>92500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>103300</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1586,114 +1640,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>107800</v>
+        <v>174800</v>
       </c>
       <c r="E26" s="3">
-        <v>113600</v>
+        <v>108600</v>
       </c>
       <c r="F26" s="3">
-        <v>88500</v>
+        <v>122600</v>
       </c>
       <c r="G26" s="3">
-        <v>72200</v>
+        <v>95100</v>
       </c>
       <c r="H26" s="3">
-        <v>110500</v>
+        <v>74300</v>
       </c>
       <c r="I26" s="3">
-        <v>251300</v>
+        <v>110400</v>
       </c>
       <c r="J26" s="3">
+        <v>226200</v>
+      </c>
+      <c r="K26" s="3">
         <v>72900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>232400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>360400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>332000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>203300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>179100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>271800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>228000</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>49000</v>
+        <v>99700</v>
       </c>
       <c r="E27" s="3">
-        <v>27300</v>
+        <v>49400</v>
       </c>
       <c r="F27" s="3">
-        <v>187700</v>
+        <v>29500</v>
       </c>
       <c r="G27" s="3">
-        <v>15600</v>
+        <v>21400</v>
       </c>
       <c r="H27" s="3">
-        <v>39900</v>
+        <v>16000</v>
       </c>
       <c r="I27" s="3">
+        <v>39800</v>
+      </c>
+      <c r="J27" s="3">
+        <v>91800</v>
+      </c>
+      <c r="K27" s="3">
+        <v>95700</v>
+      </c>
+      <c r="L27" s="3">
         <v>102000</v>
       </c>
-      <c r="J27" s="3">
-        <v>95700</v>
-      </c>
-      <c r="K27" s="3">
-        <v>102000</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>175600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>151600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>37000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>111600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>138700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>204000</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1745,13 +1808,16 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>3</v>
+      <c r="D29" s="3">
+        <v>0</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
@@ -1765,41 +1831,44 @@
       <c r="H29" s="3">
         <v>0</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>3</v>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>-198200</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>263500</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-73000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>59900</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>60700</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-37700</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1851,8 +1920,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1904,114 +1976,123 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>41000</v>
+        <v>-28500</v>
       </c>
       <c r="E32" s="3">
-        <v>-90900</v>
+        <v>-27400</v>
       </c>
       <c r="F32" s="3">
-        <v>-77900</v>
+        <v>-30200</v>
       </c>
       <c r="G32" s="3">
-        <v>-4000</v>
+        <v>-12400</v>
       </c>
       <c r="H32" s="3">
-        <v>-53700</v>
+        <v>-27900</v>
       </c>
       <c r="I32" s="3">
-        <v>-196200</v>
+        <v>-31100</v>
       </c>
       <c r="J32" s="3">
+        <v>-32500</v>
+      </c>
+      <c r="K32" s="3">
         <v>67700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-34200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-141100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-151400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>32600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-58500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-91300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-81900</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>49000</v>
+        <v>99700</v>
       </c>
       <c r="E33" s="3">
-        <v>27300</v>
+        <v>49400</v>
       </c>
       <c r="F33" s="3">
-        <v>187700</v>
+        <v>29500</v>
       </c>
       <c r="G33" s="3">
-        <v>15600</v>
+        <v>21400</v>
       </c>
       <c r="H33" s="3">
-        <v>39900</v>
+        <v>16000</v>
       </c>
       <c r="I33" s="3">
+        <v>39800</v>
+      </c>
+      <c r="J33" s="3">
+        <v>91800</v>
+      </c>
+      <c r="K33" s="3">
+        <v>-102500</v>
+      </c>
+      <c r="L33" s="3">
         <v>102000</v>
       </c>
-      <c r="J33" s="3">
-        <v>-102500</v>
-      </c>
-      <c r="K33" s="3">
-        <v>102000</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>175600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>415100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-36100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>171500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>199400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>166300</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2063,119 +2144,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>49000</v>
+        <v>99700</v>
       </c>
       <c r="E35" s="3">
-        <v>27300</v>
+        <v>49400</v>
       </c>
       <c r="F35" s="3">
-        <v>187700</v>
+        <v>29500</v>
       </c>
       <c r="G35" s="3">
-        <v>15600</v>
+        <v>21400</v>
       </c>
       <c r="H35" s="3">
-        <v>39900</v>
+        <v>16000</v>
       </c>
       <c r="I35" s="3">
+        <v>39800</v>
+      </c>
+      <c r="J35" s="3">
+        <v>91800</v>
+      </c>
+      <c r="K35" s="3">
+        <v>-102500</v>
+      </c>
+      <c r="L35" s="3">
         <v>102000</v>
       </c>
-      <c r="J35" s="3">
-        <v>-102500</v>
-      </c>
-      <c r="K35" s="3">
-        <v>102000</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>175600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>415100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-36100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>171500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>199400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>166300</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2195,8 +2285,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2216,137 +2307,144 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>4631100</v>
+        <v>4245300</v>
       </c>
       <c r="E41" s="3">
-        <v>4456400</v>
+        <v>4302400</v>
       </c>
       <c r="F41" s="3">
-        <v>4463500</v>
+        <v>4474400</v>
       </c>
       <c r="G41" s="3">
-        <v>4411700</v>
+        <v>2171600</v>
       </c>
       <c r="H41" s="3">
-        <v>4607000</v>
+        <v>4543900</v>
       </c>
       <c r="I41" s="3">
-        <v>4638700</v>
+        <v>4600000</v>
       </c>
       <c r="J41" s="3">
+        <v>4175100</v>
+      </c>
+      <c r="K41" s="3">
         <v>4087900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4503500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5574700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3937700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8794300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7896300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7478900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7377700</v>
       </c>
-      <c r="R41" s="3">
-        <v>0</v>
-      </c>
       <c r="S41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>12924200</v>
+        <v>4870700</v>
       </c>
       <c r="E42" s="3">
-        <v>12480800</v>
+        <v>4011700</v>
       </c>
       <c r="F42" s="3">
-        <v>11982100</v>
+        <v>4002400</v>
       </c>
       <c r="G42" s="3">
-        <v>11203700</v>
+        <v>3264500</v>
       </c>
       <c r="H42" s="3">
-        <v>11077200</v>
+        <v>3206000</v>
       </c>
       <c r="I42" s="3">
-        <v>10941500</v>
+        <v>3193300</v>
       </c>
       <c r="J42" s="3">
+        <v>2942300</v>
+      </c>
+      <c r="K42" s="3">
         <v>10928800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>11025600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>11083300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>9948200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>13366900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>11815200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>11196400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>10964900</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
-      </c>
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>3173600</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>3191500</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>3210800</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>2488500</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>6990700</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
+        <v>6681600</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>6018200</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2375,31 +2473,34 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+        <v>16600</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2428,31 +2529,34 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>20900</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>22300</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>26700</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>942400</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>23300</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>28200</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>21600</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2481,31 +2585,34 @@
       <c r="S45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>12659000</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>11890800</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>12052200</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>11512700</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>14763900</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>14503000</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>13157200</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2534,167 +2641,179 @@
       <c r="S46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>298200</v>
+        <v>9068100</v>
       </c>
       <c r="E47" s="3">
-        <v>269700</v>
+        <v>9308400</v>
       </c>
       <c r="F47" s="3">
-        <v>309800</v>
+        <v>9766500</v>
       </c>
       <c r="G47" s="3">
-        <v>300100</v>
+        <v>8391200</v>
       </c>
       <c r="H47" s="3">
-        <v>290700</v>
+        <v>8642400</v>
       </c>
       <c r="I47" s="3">
-        <v>285900</v>
+        <v>8157400</v>
       </c>
       <c r="J47" s="3">
+        <v>7163200</v>
+      </c>
+      <c r="K47" s="3">
         <v>341600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1373400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1269300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1045700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>281500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>236900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>222000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>203600</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
-      </c>
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1727600</v>
+        <v>1720500</v>
       </c>
       <c r="E48" s="3">
-        <v>1702700</v>
+        <v>1462300</v>
       </c>
       <c r="F48" s="3">
-        <v>1679000</v>
+        <v>1543600</v>
       </c>
       <c r="G48" s="3">
-        <v>1689300</v>
+        <v>1512300</v>
       </c>
       <c r="H48" s="3">
-        <v>1707300</v>
+        <v>1467800</v>
       </c>
       <c r="I48" s="3">
-        <v>1739500</v>
+        <v>1422500</v>
       </c>
       <c r="J48" s="3">
+        <v>1565600</v>
+      </c>
+      <c r="K48" s="3">
         <v>1736500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1781500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1831400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1680800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2184100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1943400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1863500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1891300</v>
       </c>
-      <c r="R48" s="3">
-        <v>0</v>
-      </c>
       <c r="S48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>4470200</v>
+        <v>9059700</v>
       </c>
       <c r="E49" s="3">
-        <v>4373400</v>
+        <v>9002400</v>
       </c>
       <c r="F49" s="3">
-        <v>4354100</v>
+        <v>9504600</v>
       </c>
       <c r="G49" s="3">
-        <v>4330700</v>
+        <v>9281000</v>
       </c>
       <c r="H49" s="3">
-        <v>4308000</v>
+        <v>4460400</v>
       </c>
       <c r="I49" s="3">
-        <v>4284300</v>
+        <v>4301500</v>
       </c>
       <c r="J49" s="3">
+        <v>3856100</v>
+      </c>
+      <c r="K49" s="3">
         <v>4207500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4197300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4169400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3659200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5153000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4526400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4199400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4064600</v>
       </c>
-      <c r="R49" s="3">
-        <v>0</v>
-      </c>
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2746,8 +2865,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2799,61 +2921,67 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>22200</v>
+        <v>128300</v>
       </c>
       <c r="E52" s="3">
-        <v>24700</v>
+        <v>394700</v>
       </c>
       <c r="F52" s="3">
-        <v>331700</v>
+        <v>415800</v>
       </c>
       <c r="G52" s="3">
-        <v>22600</v>
+        <v>1242000</v>
       </c>
       <c r="H52" s="3">
-        <v>28200</v>
+        <v>398500</v>
       </c>
       <c r="I52" s="3">
-        <v>24000</v>
+        <v>407500</v>
       </c>
       <c r="J52" s="3">
+        <v>131200</v>
+      </c>
+      <c r="K52" s="3">
         <v>466600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>34400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>37700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>35300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>473700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>31700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>26300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>52600</v>
       </c>
-      <c r="R52" s="3">
-        <v>0</v>
-      </c>
       <c r="S52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2905,61 +3033,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>75987700</v>
+        <v>76902800</v>
       </c>
       <c r="E54" s="3">
-        <v>73654100</v>
+        <v>76549300</v>
       </c>
       <c r="F54" s="3">
-        <v>72283600</v>
+        <v>79536600</v>
       </c>
       <c r="G54" s="3">
-        <v>71695800</v>
+        <v>77744300</v>
       </c>
       <c r="H54" s="3">
-        <v>71534800</v>
+        <v>73843200</v>
       </c>
       <c r="I54" s="3">
-        <v>71730800</v>
+        <v>71426200</v>
       </c>
       <c r="J54" s="3">
+        <v>64562300</v>
+      </c>
+      <c r="K54" s="3">
         <v>70941900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>71474100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>71788900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>62669800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>88056900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>77375100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>72292900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>70751400</v>
       </c>
-      <c r="R54" s="3">
-        <v>0</v>
-      </c>
       <c r="S54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2979,8 +3113,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3000,84 +3135,88 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>734600</v>
+        <v>47795300</v>
       </c>
       <c r="E57" s="3">
-        <v>777300</v>
+        <v>48699600</v>
       </c>
       <c r="F57" s="3">
-        <v>833800</v>
+        <v>49877100</v>
       </c>
       <c r="G57" s="3">
-        <v>658900</v>
+        <v>47873400</v>
       </c>
       <c r="H57" s="3">
-        <v>656900</v>
+        <v>45245700</v>
       </c>
       <c r="I57" s="3">
-        <v>662300</v>
+        <v>43193000</v>
       </c>
       <c r="J57" s="3">
+        <v>38526900</v>
+      </c>
+      <c r="K57" s="3">
         <v>672900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>640100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>663800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>569900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>774800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>641300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>596400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>572900</v>
       </c>
-      <c r="R57" s="3">
-        <v>0</v>
-      </c>
       <c r="S57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>5349900</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>4078600</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>4814100</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>7947000</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>4524100</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>447800</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>329000</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3106,84 +3245,90 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1754600</v>
+        <v>1920500</v>
       </c>
       <c r="E59" s="3">
-        <v>1852400</v>
+        <v>2125900</v>
       </c>
       <c r="F59" s="3">
-        <v>301600</v>
+        <v>2205100</v>
       </c>
       <c r="G59" s="3">
-        <v>1742500</v>
+        <v>695700</v>
       </c>
       <c r="H59" s="3">
-        <v>1830300</v>
+        <v>1980000</v>
       </c>
       <c r="I59" s="3">
-        <v>1964500</v>
+        <v>28400</v>
       </c>
       <c r="J59" s="3">
+        <v>1201900</v>
+      </c>
+      <c r="K59" s="3">
         <v>224300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1462100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1427000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1298500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>387400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1382400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1246800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1332200</v>
       </c>
-      <c r="R59" s="3">
-        <v>0</v>
-      </c>
       <c r="S59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>55270700</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>55199400</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>57188000</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>56812200</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>51909900</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>43669300</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>40057800</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -3212,114 +3357,123 @@
       <c r="S60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>12024500</v>
+        <v>11919900</v>
       </c>
       <c r="E61" s="3">
-        <v>11727300</v>
+        <v>12113400</v>
       </c>
       <c r="F61" s="3">
-        <v>12110300</v>
+        <v>12663900</v>
       </c>
       <c r="G61" s="3">
-        <v>12757700</v>
+        <v>9583600</v>
       </c>
       <c r="H61" s="3">
-        <v>12831400</v>
+        <v>12743000</v>
       </c>
       <c r="I61" s="3">
-        <v>14697300</v>
+        <v>16037400</v>
       </c>
       <c r="J61" s="3">
+        <v>15129400</v>
+      </c>
+      <c r="K61" s="3">
         <v>15126900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>14763300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>15120000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>12389300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>15026400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>12193300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>11352000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>11073300</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>366700</v>
+        <v>518100</v>
       </c>
       <c r="E62" s="3">
-        <v>376200</v>
+        <v>502800</v>
       </c>
       <c r="F62" s="3">
-        <v>1716600</v>
+        <v>512700</v>
       </c>
       <c r="G62" s="3">
-        <v>353700</v>
+        <v>759600</v>
       </c>
       <c r="H62" s="3">
-        <v>363800</v>
+        <v>567900</v>
       </c>
       <c r="I62" s="3">
-        <v>385000</v>
+        <v>2838100</v>
       </c>
       <c r="J62" s="3">
+        <v>2654000</v>
+      </c>
+      <c r="K62" s="3">
         <v>1621000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>390900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>404600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>393900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1462300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>348700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>332700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>339500</v>
       </c>
-      <c r="R62" s="3">
-        <v>0</v>
-      </c>
       <c r="S62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3371,8 +3525,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3424,8 +3581,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3477,61 +3637,67 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>71975000</v>
+        <v>69037700</v>
       </c>
       <c r="E66" s="3">
-        <v>69705600</v>
+        <v>68890100</v>
       </c>
       <c r="F66" s="3">
-        <v>68255700</v>
+        <v>71482700</v>
       </c>
       <c r="G66" s="3">
-        <v>67764200</v>
+        <v>69607900</v>
       </c>
       <c r="H66" s="3">
-        <v>67583100</v>
+        <v>66241000</v>
       </c>
       <c r="I66" s="3">
-        <v>67848600</v>
+        <v>64054500</v>
       </c>
       <c r="J66" s="3">
+        <v>58032800</v>
+      </c>
+      <c r="K66" s="3">
         <v>66989800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>67282400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>67519700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>58774500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>82533700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>72460600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>67787200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>66472500</v>
       </c>
-      <c r="R66" s="3">
-        <v>0</v>
-      </c>
       <c r="S66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3551,8 +3717,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3604,8 +3771,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3657,8 +3827,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3710,8 +3883,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3763,61 +3939,67 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1795700</v>
+        <v>1893300</v>
       </c>
       <c r="E72" s="3">
-        <v>1746900</v>
+        <v>1808900</v>
       </c>
       <c r="F72" s="3">
-        <v>1855600</v>
+        <v>1886400</v>
       </c>
       <c r="G72" s="3">
-        <v>1834000</v>
+        <v>1995800</v>
       </c>
       <c r="H72" s="3">
-        <v>1820300</v>
+        <v>1888900</v>
       </c>
       <c r="I72" s="3">
-        <v>1782800</v>
+        <v>1817500</v>
       </c>
       <c r="J72" s="3">
+        <v>1604700</v>
+      </c>
+      <c r="K72" s="3">
         <v>1924400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2087700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2065500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2032800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3212000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2777700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2486200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2287600</v>
       </c>
-      <c r="R72" s="3">
-        <v>0</v>
-      </c>
       <c r="S72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3869,8 +4051,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3922,8 +4107,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3975,61 +4163,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4012800</v>
+        <v>4170300</v>
       </c>
       <c r="E76" s="3">
-        <v>3948500</v>
+        <v>4042400</v>
       </c>
       <c r="F76" s="3">
-        <v>4027800</v>
+        <v>4263900</v>
       </c>
       <c r="G76" s="3">
-        <v>3931600</v>
+        <v>4332100</v>
       </c>
       <c r="H76" s="3">
-        <v>3951700</v>
+        <v>4049300</v>
       </c>
       <c r="I76" s="3">
-        <v>3882200</v>
+        <v>3945700</v>
       </c>
       <c r="J76" s="3">
+        <v>3494200</v>
+      </c>
+      <c r="K76" s="3">
         <v>3952100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4191600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4269200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3895300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5523300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4914500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4505700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4279000</v>
       </c>
-      <c r="R76" s="3">
-        <v>0</v>
-      </c>
       <c r="S76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4081,119 +4275,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>49000</v>
+        <v>99700</v>
       </c>
       <c r="E81" s="3">
-        <v>27300</v>
+        <v>49400</v>
       </c>
       <c r="F81" s="3">
-        <v>187700</v>
+        <v>29500</v>
       </c>
       <c r="G81" s="3">
-        <v>15600</v>
+        <v>21400</v>
       </c>
       <c r="H81" s="3">
-        <v>39900</v>
+        <v>16000</v>
       </c>
       <c r="I81" s="3">
+        <v>39800</v>
+      </c>
+      <c r="J81" s="3">
+        <v>91800</v>
+      </c>
+      <c r="K81" s="3">
+        <v>-102500</v>
+      </c>
+      <c r="L81" s="3">
         <v>102000</v>
       </c>
-      <c r="J81" s="3">
-        <v>-102500</v>
-      </c>
-      <c r="K81" s="3">
-        <v>102000</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>175600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>415100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-36100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>171500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>199400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>166300</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4213,61 +4416,65 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>74500</v>
+        <v>34300</v>
       </c>
       <c r="E83" s="3">
-        <v>72500</v>
+        <v>67700</v>
       </c>
       <c r="F83" s="3">
-        <v>72300</v>
+        <v>60400</v>
       </c>
       <c r="G83" s="3">
-        <v>69100</v>
+        <v>29200</v>
       </c>
       <c r="H83" s="3">
-        <v>67800</v>
+        <v>58900</v>
       </c>
       <c r="I83" s="3">
-        <v>67100</v>
+        <v>64900</v>
       </c>
       <c r="J83" s="3">
+        <v>70100</v>
+      </c>
+      <c r="K83" s="3">
         <v>68600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>67700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>70400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>63200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>89100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>80700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>73900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>74800</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
       <c r="S83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4319,8 +4526,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4372,8 +4582,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4425,8 +4638,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4478,8 +4694,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4531,61 +4750,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-201500</v>
+        <v>203900</v>
       </c>
       <c r="E89" s="3">
-        <v>666500</v>
+        <v>-1846100</v>
       </c>
       <c r="F89" s="3">
-        <v>678200</v>
+        <v>-1105100</v>
       </c>
       <c r="G89" s="3">
-        <v>292200</v>
+        <v>-345700</v>
       </c>
       <c r="H89" s="3">
-        <v>297600</v>
+        <v>88800</v>
       </c>
       <c r="I89" s="3">
-        <v>173300</v>
+        <v>-847100</v>
       </c>
       <c r="J89" s="3">
+        <v>-1043600</v>
+      </c>
+      <c r="K89" s="3">
         <v>-998500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-333000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1538000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-489300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>495500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-21700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>505500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>321100</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
       <c r="S89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4605,61 +4830,65 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-315041000</v>
+        <v>-31500</v>
       </c>
       <c r="E91" s="3">
-        <v>-284289000</v>
+        <v>-42200</v>
       </c>
       <c r="F91" s="3">
-        <v>-441443000</v>
+        <v>-38000</v>
       </c>
       <c r="G91" s="3">
-        <v>-394006000</v>
+        <v>-59700</v>
       </c>
       <c r="H91" s="3">
-        <v>-257519000</v>
+        <v>-33700</v>
       </c>
       <c r="I91" s="3">
-        <v>-205678000</v>
+        <v>-37900</v>
       </c>
       <c r="J91" s="3">
+        <v>-19400</v>
+      </c>
+      <c r="K91" s="3">
         <v>-482508000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-281054000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-238582000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-143769000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-489803000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-299606000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-24200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-16300</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4711,8 +4940,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4764,61 +4996,67 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>101100</v>
+        <v>242200</v>
       </c>
       <c r="E94" s="3">
-        <v>-424800</v>
+        <v>101900</v>
       </c>
       <c r="F94" s="3">
-        <v>-17900</v>
+        <v>-458700</v>
       </c>
       <c r="G94" s="3">
-        <v>-222200</v>
+        <v>-19300</v>
       </c>
       <c r="H94" s="3">
-        <v>55000</v>
+        <v>-228900</v>
       </c>
       <c r="I94" s="3">
-        <v>626900</v>
+        <v>54900</v>
       </c>
       <c r="J94" s="3">
+        <v>564200</v>
+      </c>
+      <c r="K94" s="3">
         <v>662200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>345800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>47900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4161400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-522800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>67100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-178900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-814100</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4838,61 +5076,65 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-33900</v>
+        <v>33900</v>
       </c>
       <c r="E96" s="3">
-        <v>-61200</v>
+        <v>34200</v>
       </c>
       <c r="F96" s="3">
-        <v>-61200</v>
+        <v>66100</v>
       </c>
       <c r="G96" s="3">
-        <v>-61200</v>
+        <v>65800</v>
       </c>
       <c r="H96" s="3">
-        <v>-61200</v>
+        <v>63000</v>
       </c>
       <c r="I96" s="3">
-        <v>-400</v>
+        <v>61100</v>
       </c>
       <c r="J96" s="3">
+        <v>300</v>
+      </c>
+      <c r="K96" s="3">
         <v>-500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-28600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-72000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-72100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-66000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-62900</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-69500</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4944,8 +5186,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4997,8 +5242,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5050,163 +5298,175 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-523100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>1660900</v>
+      </c>
+      <c r="F100" s="3">
+        <v>1521100</v>
+      </c>
+      <c r="G100" s="3">
+        <v>808000</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-27500</v>
+      </c>
+      <c r="I100" s="3">
+        <v>934200</v>
+      </c>
+      <c r="J100" s="3">
+        <v>1058000</v>
+      </c>
+      <c r="K100" s="3">
+        <v>-573100</v>
+      </c>
+      <c r="L100" s="3">
+        <v>-1186700</v>
+      </c>
+      <c r="M100" s="3">
+        <v>-276100</v>
+      </c>
+      <c r="N100" s="3">
+        <v>-89700</v>
+      </c>
+      <c r="O100" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="P100" s="3">
+        <v>-57600</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>-229100</v>
+      </c>
+      <c r="R100" s="3">
         <v>17700</v>
       </c>
-      <c r="E100" s="3">
-        <v>-281200</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-248400</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-232700</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-210300</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-157400</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-573100</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-1186700</v>
-      </c>
-      <c r="L100" s="3">
-        <v>-276100</v>
-      </c>
-      <c r="M100" s="3">
-        <v>-89700</v>
-      </c>
-      <c r="N100" s="3">
-        <v>-18500</v>
-      </c>
-      <c r="O100" s="3">
-        <v>-57600</v>
-      </c>
-      <c r="P100" s="3">
-        <v>-229100</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>17700</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>257400</v>
+        <v>-33400</v>
       </c>
       <c r="E101" s="3">
-        <v>32500</v>
+        <v>-173700</v>
       </c>
       <c r="F101" s="3">
-        <v>-360100</v>
+        <v>-82900</v>
       </c>
       <c r="G101" s="3">
-        <v>-32500</v>
+        <v>579300</v>
       </c>
       <c r="H101" s="3">
-        <v>-174000</v>
+        <v>275700</v>
       </c>
       <c r="I101" s="3">
-        <v>-92100</v>
+        <v>-900</v>
       </c>
       <c r="J101" s="3">
+        <v>-128900</v>
+      </c>
+      <c r="K101" s="3">
         <v>673900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>317100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-116100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>226000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>73500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>3600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>707700</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>174700</v>
+        <v>-34600</v>
       </c>
       <c r="E102" s="3">
-        <v>-7100</v>
+        <v>176000</v>
       </c>
       <c r="F102" s="3">
-        <v>51700</v>
+        <v>-7700</v>
       </c>
       <c r="G102" s="3">
-        <v>-195200</v>
+        <v>55600</v>
       </c>
       <c r="H102" s="3">
+        <v>-201100</v>
+      </c>
+      <c r="I102" s="3">
         <v>-31700</v>
       </c>
-      <c r="I102" s="3">
-        <v>550800</v>
-      </c>
       <c r="J102" s="3">
+        <v>495800</v>
+      </c>
+      <c r="K102" s="3">
         <v>-235500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-856800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1308800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-4856600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>180100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>61300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>101100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>232400</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
       <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AVAL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AVAL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="92">
   <si>
     <t>AVAL</t>
   </si>
@@ -656,148 +656,154 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="17" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>676400</v>
+      </c>
+      <c r="E8" s="3">
         <v>748900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>690000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>720200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>694700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>604100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>701300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>789000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1474500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1303200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1114500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>902300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>578700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>707300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>660300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>653500</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -852,35 +858,38 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>676400</v>
+      </c>
+      <c r="E10" s="3">
         <v>748900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>690000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>720200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>694700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>604100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>701300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>789000</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -908,8 +917,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -930,8 +942,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -986,8 +999,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1042,32 +1058,35 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E14" s="3">
         <v>-2400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-4100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-2100</v>
       </c>
-      <c r="G14" s="3">
-        <v>-38600</v>
-      </c>
       <c r="H14" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="I14" s="3">
         <v>-3500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>7100</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
@@ -1092,70 +1111,76 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>60100</v>
+      </c>
+      <c r="E15" s="3">
         <v>61900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>42000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>78300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>61100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>55900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>38500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>60400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-68600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-67700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-70400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-63200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-62600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-57200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-52400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-52900</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1173,120 +1198,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>509200</v>
+      </c>
+      <c r="E17" s="3">
         <v>465800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>482000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>510900</v>
       </c>
-      <c r="G17" s="3">
-        <v>561000</v>
-      </c>
       <c r="H17" s="3">
+        <v>545600</v>
+      </c>
+      <c r="I17" s="3">
         <v>461800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>468700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>415300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1207500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>968100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>748600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>569900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>251700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>364100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>387300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>404100</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>167300</v>
+      </c>
+      <c r="E18" s="3">
         <v>283100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>208000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>209300</v>
       </c>
-      <c r="G18" s="3">
-        <v>133700</v>
-      </c>
       <c r="H18" s="3">
+        <v>149100</v>
+      </c>
+      <c r="I18" s="3">
         <v>142200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>232500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>373700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>266900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>335100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>366000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>332400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>326900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>343200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>273000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>249400</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1307,120 +1339,127 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E20" s="3">
         <v>28500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>27400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>30200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>12400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>27900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>31100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>32500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-67700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>34200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>141100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>151400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-32600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>58500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>91300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>81900</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>198800</v>
+      </c>
+      <c r="E21" s="3">
         <v>316400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>222600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>257300</v>
       </c>
-      <c r="G21" s="3">
-        <v>182400</v>
-      </c>
       <c r="H21" s="3">
+        <v>197800</v>
+      </c>
+      <c r="I21" s="3">
         <v>170200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>239900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>401700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>267800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>437100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>577500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>547100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>383500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>482300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>438200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>406100</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1445,8 +1484,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1469,126 +1508,135 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>136900</v>
+      </c>
+      <c r="E23" s="3">
         <v>256900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>184800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>181100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>160000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>117900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>194400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>341300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>199300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>369400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>507100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>483900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>294300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>401700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>364300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>331300</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E24" s="3">
         <v>82100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>76200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>58500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>64800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>43600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>84000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>115000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>126300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>137000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>146700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>151900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>91000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>222600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>92500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>103300</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1643,120 +1691,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>122600</v>
+      </c>
+      <c r="E26" s="3">
         <v>174800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>108600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>122600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>95100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>74300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>110400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>226200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>72900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>232400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>360400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>332000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>203300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>179100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>271800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>228000</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>63800</v>
+      </c>
+      <c r="E27" s="3">
         <v>99700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>49400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>29500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>21400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>16000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>39800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>91800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>95700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>102000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>175600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>151600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>37000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>111600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>138700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>204000</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1811,8 +1868,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1838,37 +1898,40 @@
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>-198200</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>263500</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-73000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>59900</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>60700</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-37700</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1923,8 +1986,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1979,120 +2045,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-28600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-28500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-27400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-30200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-12400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-27900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-31100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-32500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>67700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-34200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-141100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-151400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>32600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-58500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-91300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-81900</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>63800</v>
+      </c>
+      <c r="E33" s="3">
         <v>99700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>49400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>29500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>21400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>16000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>39800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>91800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-102500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>102000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>175600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>415100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-36100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>171500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>199400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>166300</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2147,125 +2222,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>63800</v>
+      </c>
+      <c r="E35" s="3">
         <v>99700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>49400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>29500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>21400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>16000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>39800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>91800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-102500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>102000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>175600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>415100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-36100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>171500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>199400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>166300</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2286,8 +2370,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2308,147 +2393,154 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1650700</v>
+      </c>
+      <c r="E41" s="3">
         <v>4245300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4302400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4474400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2171600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4543900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4600000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4175100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4087900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4503500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5574700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3937700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8794300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7896300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7478900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7377700</v>
       </c>
-      <c r="S41" s="3">
-        <v>0</v>
-      </c>
       <c r="T41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3121600</v>
+      </c>
+      <c r="E42" s="3">
         <v>4870700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4011700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>4002400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3264500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3206000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3193300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2942300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>10928800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>11025600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>11083300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>9948200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>13366900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>11815200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>11196400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>10964900</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
-      </c>
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2489200</v>
+      </c>
+      <c r="E43" s="3">
         <v>3173600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3191500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3210800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2488500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6990700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6681600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6018200</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
         <v>0</v>
       </c>
@@ -2476,13 +2568,16 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>3</v>
+      <c r="D44" s="3">
+        <v>17700</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>3</v>
@@ -2490,20 +2585,20 @@
       <c r="F44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3">
         <v>16600</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2532,35 +2627,38 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1667000</v>
+      </c>
+      <c r="E45" s="3">
         <v>20900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>22300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>26700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>942400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>23300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>28200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>21600</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -2588,35 +2686,38 @@
       <c r="T45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>11150500</v>
+      </c>
+      <c r="E46" s="3">
         <v>12659000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>11890800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12052200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>11512700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>14763900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>14503000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>13157200</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2644,176 +2745,188 @@
       <c r="T46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>8547300</v>
+      </c>
+      <c r="E47" s="3">
         <v>9068100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>9308400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>9766500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>8391200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>8642400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>8157400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>7163200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>341600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1373400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1269300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1045700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>281500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>236900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>222000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>203600</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
-      </c>
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1368000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1720500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1462300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1543600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1512300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1467800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1422500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1565600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1736500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1781500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1831400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1680800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2184100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1943400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1863500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1891300</v>
       </c>
-      <c r="S48" s="3">
-        <v>0</v>
-      </c>
       <c r="T48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8743800</v>
+      </c>
+      <c r="E49" s="3">
         <v>9059700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9002400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9504600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9281000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4460400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4301500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3856100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4207500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4197300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4169400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3659200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5153000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4526400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4199400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4064600</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
-      </c>
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2868,8 +2981,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2924,64 +3040,70 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1055200</v>
+      </c>
+      <c r="E52" s="3">
         <v>128300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>394700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>415800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1242000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>398500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>407500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>131200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>466600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>34400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>37700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>35300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>473700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>31700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>26300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>52600</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
-      </c>
       <c r="T52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3036,64 +3158,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>74351300</v>
+      </c>
+      <c r="E54" s="3">
         <v>76902800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>76549300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>79536600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>77744300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>73843200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>71426200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>64562300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>70941900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>71474100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>71788900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>62669800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>88056900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>77375100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>72292900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>70751400</v>
       </c>
-      <c r="S54" s="3">
-        <v>0</v>
-      </c>
       <c r="T54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3114,8 +3242,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3136,91 +3265,95 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>46291200</v>
+      </c>
+      <c r="E57" s="3">
         <v>47795300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>48699600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>49877100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>47873400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>45245700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>43193000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>38526900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>672900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>640100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>663800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>569900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>774800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>641300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>596400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>572900</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
-      </c>
       <c r="T57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6318400</v>
+      </c>
+      <c r="E58" s="3">
         <v>5349900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4078600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4814100</v>
       </c>
-      <c r="G58" s="3">
-        <v>7947000</v>
-      </c>
       <c r="H58" s="3">
+        <v>6612400</v>
+      </c>
+      <c r="I58" s="3">
         <v>4524100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>447800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>329000</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -3248,91 +3381,97 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>542300</v>
+      </c>
+      <c r="E59" s="3">
         <v>1920500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2125900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2205100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>695700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1980000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>28400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1201900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>224300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1462100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1427000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1298500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>387400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1382400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1246800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1332200</v>
       </c>
-      <c r="S59" s="3">
-        <v>0</v>
-      </c>
       <c r="T59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>53451400</v>
+      </c>
+      <c r="E60" s="3">
         <v>55270700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>55199400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>57188000</v>
       </c>
-      <c r="G60" s="3">
-        <v>56812200</v>
-      </c>
       <c r="H60" s="3">
+        <v>55477600</v>
+      </c>
+      <c r="I60" s="3">
         <v>51909900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>43669300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>40057800</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -3360,120 +3499,129 @@
       <c r="T60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10430800</v>
+      </c>
+      <c r="E61" s="3">
         <v>11919900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>12113400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>12663900</v>
       </c>
-      <c r="G61" s="3">
-        <v>9583600</v>
-      </c>
       <c r="H61" s="3">
+        <v>10918200</v>
+      </c>
+      <c r="I61" s="3">
         <v>12743000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>16037400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>15129400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>15126900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>14763300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>15120000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>12389300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>15026400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>12193300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>11352000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>11073300</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>563400</v>
+      </c>
+      <c r="E62" s="3">
         <v>518100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>502800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>512700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>759600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>567900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2838100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2654000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1621000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>390900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>404600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>393900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1462300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>348700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>332700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>339500</v>
       </c>
-      <c r="S62" s="3">
-        <v>0</v>
-      </c>
       <c r="T62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3528,8 +3676,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3584,8 +3735,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3640,64 +3794,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>66830700</v>
+      </c>
+      <c r="E66" s="3">
         <v>69037700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>68890100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>71482700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>69607900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>66241000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>64054500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>58032800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>66989800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>67282400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>67519700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>58774500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>82533700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>72460600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>67787200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>66472500</v>
       </c>
-      <c r="S66" s="3">
-        <v>0</v>
-      </c>
       <c r="T66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3718,8 +3878,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3774,8 +3935,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3830,8 +3994,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3886,8 +4053,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3942,64 +4112,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1851300</v>
+      </c>
+      <c r="E72" s="3">
         <v>1893300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1808900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1886400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1995800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1888900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1817500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1604700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1924400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2087700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2065500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2032800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3212000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2777700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2486200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2287600</v>
       </c>
-      <c r="S72" s="3">
-        <v>0</v>
-      </c>
       <c r="T72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4054,8 +4230,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4110,8 +4289,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4166,64 +4348,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3957600</v>
+      </c>
+      <c r="E76" s="3">
         <v>4170300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4042400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4263900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4332100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4049300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3945700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3494200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3952100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4191600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4269200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3895300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5523300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4914500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4505700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4279000</v>
       </c>
-      <c r="S76" s="3">
-        <v>0</v>
-      </c>
       <c r="T76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4278,125 +4466,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>63800</v>
+      </c>
+      <c r="E81" s="3">
         <v>99700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>49400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>29500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>21400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>16000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>39800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>91800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-102500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>102000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>175600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>415100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-36100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>171500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>199400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>166300</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4417,64 +4614,68 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>36500</v>
+      </c>
+      <c r="E83" s="3">
         <v>34300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>67700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>60400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>29200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>58900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>64900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>70100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>68600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>67700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>70400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>63200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>89100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>80700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>73900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>74800</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4529,8 +4730,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4585,8 +4789,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4641,8 +4848,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4697,8 +4907,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4753,64 +4966,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-678600</v>
+      </c>
+      <c r="E89" s="3">
         <v>203900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1846100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1105100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-345700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>88800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-847100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1043600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-998500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-333000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1538000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-489300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>495500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-21700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>505500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>321100</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
       <c r="T89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4831,64 +5050,68 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-47700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-31500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-42200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-38000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-59700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-33700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-37900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-19400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-482508000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-281054000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-238582000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-143769000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-489803000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-299606000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-24200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-16300</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4943,8 +5166,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4999,64 +5225,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-635700</v>
+      </c>
+      <c r="E94" s="3">
         <v>242200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>101900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-458700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-19300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-228900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>54900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>564200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>662200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>345800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>47900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4161400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-522800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>67100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-178900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-814100</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5077,64 +5309,68 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>43100</v>
+      </c>
+      <c r="E96" s="3">
         <v>33900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>34200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>66100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>65800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>63000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>61100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-28600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-72000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-72100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-66000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-62900</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-69500</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5189,8 +5425,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5245,8 +5484,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5301,172 +5543,184 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>658300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-523100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1660900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1521100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>808000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-27500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>934200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1058000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-573100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1186700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-276100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-89700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-18500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-57600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-229100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>17700</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-387300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-33400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-173700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-82900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>579300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>275700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-128900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>673900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>317100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-116100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>226000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>73500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>3600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>707700</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-488300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-34600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>176000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-7700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>55600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-201100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-31700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>495800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-235500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-856800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1308800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-4856600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>180100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>61300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>101100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>232400</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
       <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AVAL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AVAL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
   <si>
     <t>AVAL</t>
   </si>
@@ -656,154 +656,161 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>817000</v>
+      </c>
+      <c r="E8" s="3">
         <v>676400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>748900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>690000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>720200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>694700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>604100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>701300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>789000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1474500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1303200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1114500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>902300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>578700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>707300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>660300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>653500</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -861,38 +868,41 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>817000</v>
+      </c>
+      <c r="E10" s="3">
         <v>676400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>748900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>690000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>720200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>694700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>604100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>701300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>789000</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -920,8 +930,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -943,8 +956,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1002,8 +1016,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1061,35 +1078,38 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E14" s="3">
         <v>1800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-2400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-4100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-2100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-23300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-3500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>7100</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1114,73 +1134,79 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>59500</v>
+      </c>
+      <c r="E15" s="3">
         <v>60100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>61900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>42000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>78300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>61100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>55900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>38500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>60400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-68600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-67700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-70400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-63200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-62600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-57200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-52400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-52900</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1199,126 +1225,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>537400</v>
+      </c>
+      <c r="E17" s="3">
         <v>509200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>465800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>482000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>510900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>545600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>461800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>468700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>415300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1207500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>968100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>748600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>569900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>251700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>364100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>387300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>404100</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>279600</v>
+      </c>
+      <c r="E18" s="3">
         <v>167300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>283100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>208000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>209300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>149100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>142200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>232500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>373700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>266900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>335100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>366000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>332400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>326900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>343200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>273000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>249400</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1340,126 +1373,133 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
         <v>28600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>28500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>27400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>30200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>12400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>27900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>31100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>32500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-67700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>34200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>141100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>151400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-32600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>58500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>91300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>81900</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>339100</v>
+      </c>
+      <c r="E21" s="3">
         <v>198800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>316400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>222600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>257300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>197800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>170200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>239900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>401700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>267800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>437100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>577500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>547100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>383500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>482300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>438200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>406100</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1487,8 +1527,8 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1511,132 +1551,141 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
+      <c r="T22" s="3">
+        <v>0</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>281400</v>
+      </c>
+      <c r="E23" s="3">
         <v>136900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>256900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>184800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>181100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>160000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>117900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>194400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>341300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>199300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>369400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>507100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>483900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>294300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>401700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>364300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>331300</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>90400</v>
+      </c>
+      <c r="E24" s="3">
         <v>14300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>82100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>76200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>58500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>64800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>43600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>84000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>115000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>126300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>137000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>146700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>151900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>91000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>222600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>92500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>103300</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1694,126 +1743,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>191100</v>
+      </c>
+      <c r="E26" s="3">
         <v>122600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>174800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>108600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>122600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>95100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>74300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>110400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>226200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>72900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>232400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>360400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>332000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>203300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>179100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>271800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>228000</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>86200</v>
+      </c>
+      <c r="E27" s="3">
         <v>63800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>99700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>49400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>29500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>21400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>16000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>39800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>91800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>95700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>102000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>175600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>151600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>37000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>111600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>138700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>204000</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1871,8 +1929,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1901,37 +1962,40 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-198200</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>263500</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-73000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>59900</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>60700</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-37700</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1989,8 +2053,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2048,126 +2115,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
         <v>-28600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-28500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-27400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-30200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-12400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-27900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-31100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-32500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>67700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-34200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-141100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-151400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>32600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-58500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-91300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-81900</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>86200</v>
+      </c>
+      <c r="E33" s="3">
         <v>63800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>99700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>49400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>29500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>21400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>16000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>39800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>91800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-102500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>102000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>175600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>415100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-36100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>171500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>199400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>166300</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2225,131 +2301,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>86200</v>
+      </c>
+      <c r="E35" s="3">
         <v>63800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>99700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>49400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>29500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>21400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>16000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>39800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>91800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-102500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>102000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>175600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>415100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-36100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>171500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>199400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>166300</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2371,8 +2456,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2394,156 +2480,163 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4563300</v>
+      </c>
+      <c r="E41" s="3">
         <v>1650700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4245300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4302400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4474400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2171600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4543900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4600000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4175100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4087900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4503500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5574700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3937700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8794300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7896300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7478900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7377700</v>
       </c>
-      <c r="T41" s="3">
-        <v>0</v>
-      </c>
       <c r="U41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4987800</v>
+      </c>
+      <c r="E42" s="3">
         <v>3121600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4870700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>4011700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>4002400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3264500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3206000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3193300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2942300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>10928800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>11025600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>11083300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>9948200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>13366900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>11815200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>11196400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>10964900</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
-      </c>
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7071500</v>
+      </c>
+      <c r="E43" s="3">
         <v>2489200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3173600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3191500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3210800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2488500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6990700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6681600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6018200</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
@@ -2571,37 +2664,40 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3">
         <v>17700</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3">
         <v>16600</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2630,38 +2726,41 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E45" s="3">
         <v>1667000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>20900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>22300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>26700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>942400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>23300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>28200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>21600</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -2689,38 +2788,41 @@
       <c r="U45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>16645300</v>
+      </c>
+      <c r="E46" s="3">
         <v>11150500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12659000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>11890800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>12052200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11512700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>14763900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>14503000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>13157200</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2748,185 +2850,197 @@
       <c r="U46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>9905000</v>
+      </c>
+      <c r="E47" s="3">
         <v>8547300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>9068100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>9308400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>9766500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>8391200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>8642400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>8157400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>7163200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>341600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1373400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1269300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1045700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>281500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>236900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>222000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>203600</v>
       </c>
-      <c r="T47" s="3">
-        <v>0</v>
-      </c>
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1430200</v>
+      </c>
+      <c r="E48" s="3">
         <v>1368000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1720500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1462300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1543600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1512300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1467800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1422500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1565600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1736500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1781500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1831400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1680800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2184100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1943400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1863500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1891300</v>
       </c>
-      <c r="T48" s="3">
-        <v>0</v>
-      </c>
       <c r="U48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4570500</v>
+      </c>
+      <c r="E49" s="3">
         <v>8743800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9059700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9002400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9504600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9281000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4460400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4301500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3856100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4207500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4197300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4169400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3659200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5153000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4526400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4199400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4064600</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
-      </c>
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2984,8 +3098,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3043,67 +3160,73 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>442600</v>
+      </c>
+      <c r="E52" s="3">
         <v>1055200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>128300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>394700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>415800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1242000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>398500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>407500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>131200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>466600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>34400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>37700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>35300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>473700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>31700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>26300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>52600</v>
       </c>
-      <c r="T52" s="3">
-        <v>0</v>
-      </c>
       <c r="U52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3161,67 +3284,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>78648100</v>
+      </c>
+      <c r="E54" s="3">
         <v>74351300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>76902800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>76549300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>79536600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>77744300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>73843200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>71426200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>64562300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>70941900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>71474100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>71788900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>62669800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>88056900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>77375100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>72292900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>70751400</v>
       </c>
-      <c r="T54" s="3">
-        <v>0</v>
-      </c>
       <c r="U54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3243,8 +3372,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3266,97 +3396,101 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>49547900</v>
+      </c>
+      <c r="E57" s="3">
         <v>46291200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>47795300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>48699600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>49877100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>47873400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>45245700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>43193000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>38526900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>672900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>640100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>663800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>569900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>774800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>641300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>596400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>572900</v>
       </c>
-      <c r="T57" s="3">
-        <v>0</v>
-      </c>
       <c r="U57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4344400</v>
+      </c>
+      <c r="E58" s="3">
         <v>6318400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5349900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4078600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4814100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6612400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4524100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>447800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>329000</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -3384,97 +3518,103 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>72900</v>
+      </c>
+      <c r="E59" s="3">
         <v>542300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1920500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2125900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2205100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>695700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1980000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>28400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1201900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>224300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1462100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1427000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1298500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>387400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1382400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1246800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1332200</v>
       </c>
-      <c r="T59" s="3">
-        <v>0</v>
-      </c>
       <c r="U59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>53965200</v>
+      </c>
+      <c r="E60" s="3">
         <v>53451400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>55270700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>55199400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>57188000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>55477600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>51909900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>43669300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>40057800</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -3502,126 +3642,135 @@
       <c r="U60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>12255200</v>
+      </c>
+      <c r="E61" s="3">
         <v>10430800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>11919900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>12113400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12663900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>10918200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12743000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>16037400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>15129400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>15126900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>14763300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>15120000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>12389300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>15026400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>12193300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>11352000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>11073300</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3049100</v>
+      </c>
+      <c r="E62" s="3">
         <v>563400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>518100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>502800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>512700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>759600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>567900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2838100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2654000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1621000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>390900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>404600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>393900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1462300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>348700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>332700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>339500</v>
       </c>
-      <c r="T62" s="3">
-        <v>0</v>
-      </c>
       <c r="U62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3679,8 +3828,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3738,8 +3890,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3797,67 +3952,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>70867300</v>
+      </c>
+      <c r="E66" s="3">
         <v>66830700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>69037700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>68890100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>71482700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>69607900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>66241000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>64054500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>58032800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>66989800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>67282400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>67519700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>58774500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>82533700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>72460600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>67787200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>66472500</v>
       </c>
-      <c r="T66" s="3">
-        <v>0</v>
-      </c>
       <c r="U66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3879,8 +4040,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3938,8 +4100,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3997,8 +4162,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4056,8 +4224,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4115,67 +4286,73 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" s="3">
         <v>1851300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1893300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1808900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1886400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1995800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1888900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1817500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1604700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1924400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2087700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2065500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2032800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3212000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2777700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2486200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2287600</v>
       </c>
-      <c r="T72" s="3">
-        <v>0</v>
-      </c>
       <c r="U72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4233,8 +4410,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4292,8 +4472,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4351,67 +4534,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4094600</v>
+      </c>
+      <c r="E76" s="3">
         <v>3957600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4170300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4042400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4263900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4332100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4049300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3945700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3494200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3952100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4191600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4269200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3895300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5523300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4914500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4505700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4279000</v>
       </c>
-      <c r="T76" s="3">
-        <v>0</v>
-      </c>
       <c r="U76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4469,131 +4658,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>86200</v>
+      </c>
+      <c r="E81" s="3">
         <v>63800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>99700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>49400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>29500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>21400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>16000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>39800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>91800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-102500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>102000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>175600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>415100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-36100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>171500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>199400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>166300</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4615,67 +4813,71 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>78300</v>
+      </c>
+      <c r="E83" s="3">
         <v>36500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>34300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>67700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>60400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>29200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>58900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>64900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>70100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>68600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>67700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>70400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>63200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>89100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>80700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>73900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>74800</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
-      </c>
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4733,8 +4935,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4792,8 +4997,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4851,8 +5059,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4910,8 +5121,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4969,67 +5183,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" s="3">
         <v>-678600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>203900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1846100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1105100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-345700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>88800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-847100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1043600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-998500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-333000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1538000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-489300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>495500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-21700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>505500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>321100</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
       <c r="U89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5051,67 +5271,71 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3">
         <v>-47700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-31500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-42200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-38000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-59700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-33700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-37900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-19400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-482508000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-281054000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-238582000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-143769000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-489803000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-299606000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-24200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-16300</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5169,8 +5393,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5228,67 +5455,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3">
         <v>-635700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>242200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>101900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-458700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-19300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-228900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>54900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>564200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>662200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>345800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>47900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4161400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-522800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>67100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-178900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-814100</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5310,67 +5543,71 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3">
         <v>43100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>33900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>34200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>66100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>65800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>63000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>61100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-28600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-72000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-72100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-66000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-62900</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-69500</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5428,8 +5665,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5487,8 +5727,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5546,181 +5789,193 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3">
         <v>658300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-523100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1660900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1521100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>808000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-27500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>934200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1058000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-573100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1186700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-276100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-89700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-18500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-57600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-229100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>17700</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>35100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-387300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-33400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-173700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-82900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>579300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>275700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-128900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>673900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>317100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-116100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>226000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>73500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>3600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>707700</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-488300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-34600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>176000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-7700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>55600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-201100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-31700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>495800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-235500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-856800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1308800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4856600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>180100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>61300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>101100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>232400</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
       <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AVAL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AVAL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
   <si>
     <t>AVAL</t>
   </si>
@@ -656,161 +656,168 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="18" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="19" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>817000</v>
+        <v>865700</v>
       </c>
       <c r="E8" s="3">
+        <v>815400</v>
+      </c>
+      <c r="F8" s="3">
         <v>676400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>748900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>690000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>720200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>694700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>604100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>701300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>789000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1474500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1303200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1114500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>902300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>578700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>707300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>660300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>653500</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -871,41 +878,44 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>817000</v>
+        <v>865700</v>
       </c>
       <c r="E10" s="3">
+        <v>815400</v>
+      </c>
+      <c r="F10" s="3">
         <v>676400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>748900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>690000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>720200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>694700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>604100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>701300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>789000</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -933,8 +943,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -957,8 +970,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1019,8 +1033,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1081,38 +1098,41 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E14" s="3">
         <v>-1900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-2400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-4100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-2100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-23300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-3500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>7100</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1137,76 +1157,82 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>66600</v>
+      </c>
+      <c r="E15" s="3">
         <v>59500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>60100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>61900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>42000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>78300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>61100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>55900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>38500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>60400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-68600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-67700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-70400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-63200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-62600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-57200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-52400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-52900</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1226,132 +1252,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>537400</v>
+        <v>524100</v>
       </c>
       <c r="E17" s="3">
+        <v>503600</v>
+      </c>
+      <c r="F17" s="3">
         <v>509200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>465800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>482000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>510900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>545600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>461800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>468700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>415300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1207500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>968100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>748600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>569900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>251700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>364100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>387300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>404100</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>279600</v>
+        <v>341600</v>
       </c>
       <c r="E18" s="3">
+        <v>311800</v>
+      </c>
+      <c r="F18" s="3">
         <v>167300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>283100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>208000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>209300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>149100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>142200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>232500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>373700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>266900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>335100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>366000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>332400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>326900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>343200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>273000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>249400</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1374,132 +1407,139 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>34600</v>
       </c>
       <c r="E20" s="3">
+        <v>32300</v>
+      </c>
+      <c r="F20" s="3">
         <v>28600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>28500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>27400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>30200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>12400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>27900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>31100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>32500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-67700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>34200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>141100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>151400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-32600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>58500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>91300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>81900</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>373600</v>
+      </c>
+      <c r="E21" s="3">
         <v>339100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>198800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>316400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>222600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>257300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>197800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>170200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>239900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>401700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>267800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>437100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>577500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>547100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>383500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>482300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>438200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>406100</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1530,8 +1570,8 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1554,138 +1594,147 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
+      <c r="U22" s="3">
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>310400</v>
+      </c>
+      <c r="E23" s="3">
         <v>281400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>136900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>256900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>184800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>181100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>160000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>117900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>194400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>341300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>199300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>369400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>507100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>483900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>294300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>401700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>364300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>331300</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>94000</v>
+      </c>
+      <c r="E24" s="3">
         <v>90400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>14300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>82100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>76200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>58500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>64800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>43600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>84000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>115000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>126300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>137000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>146700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>151900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>91000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>222600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>92500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>103300</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1746,132 +1795,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>216400</v>
+      </c>
+      <c r="E26" s="3">
         <v>191100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>122600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>174800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>108600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>122600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>95100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>74300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>110400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>226200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>72900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>232400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>360400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>332000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>203300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>179100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>271800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>228000</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>121200</v>
+      </c>
+      <c r="E27" s="3">
         <v>86200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>63800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>99700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>49400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>29500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>21400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>16000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>39800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>91800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>95700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>102000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>175600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>151600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>37000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>111600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>138700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>204000</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1932,8 +1990,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1965,37 +2026,40 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-198200</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
       <c r="O29" s="3">
         <v>0</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>263500</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-73000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>59900</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>60700</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-37700</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2056,8 +2120,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2118,132 +2185,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>-34600</v>
       </c>
       <c r="E32" s="3">
+        <v>-32300</v>
+      </c>
+      <c r="F32" s="3">
         <v>-28600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-28500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-27400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-30200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-12400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-27900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-31100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-32500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>67700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-34200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-141100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-151400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>32600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-58500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-91300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-81900</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>121200</v>
+      </c>
+      <c r="E33" s="3">
         <v>86200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>63800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>99700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>49400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>29500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>21400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>16000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>39800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>91800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-102500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>102000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>175600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>415100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-36100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>171500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>199400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>166300</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2304,137 +2380,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>121200</v>
+      </c>
+      <c r="E35" s="3">
         <v>86200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>63800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>99700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>49400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>29500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>21400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>16000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>39800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>91800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-102500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>102000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>175600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>415100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-36100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>171500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>199400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>166300</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2457,8 +2542,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2481,165 +2567,172 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4453300</v>
+      </c>
+      <c r="E41" s="3">
         <v>4563300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1650700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4245300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4302400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4474400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2171600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4543900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4600000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4175100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4087900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4503500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5574700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3937700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8794300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7896300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7478900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7377700</v>
       </c>
-      <c r="U41" s="3">
-        <v>0</v>
-      </c>
       <c r="V41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>6050900</v>
+      </c>
+      <c r="E42" s="3">
         <v>4987800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3121600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>4870700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>4011700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>4002400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3264500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3206000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>3193300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2942300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>10928800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>11025600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>11083300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>9948200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>13366900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>11815200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>11196400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>10964900</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
-      </c>
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3367500</v>
+      </c>
+      <c r="E43" s="3">
         <v>7071500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2489200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3173600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3191500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3210800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2488500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6990700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6681600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6018200</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
       <c r="N43" s="3">
         <v>0</v>
       </c>
@@ -2667,40 +2760,43 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3">
         <v>17700</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3">
         <v>16600</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2729,41 +2825,44 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E45" s="3">
         <v>22700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1667000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>20900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>22300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>26700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>942400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>23300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>28200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>21600</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
       <c r="N45" s="3">
         <v>0</v>
       </c>
@@ -2791,41 +2890,44 @@
       <c r="V45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13998200</v>
+      </c>
+      <c r="E46" s="3">
         <v>16645300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>11150500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12659000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>11890800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12052200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11512700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>14763900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>14503000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>13157200</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -2853,194 +2955,206 @@
       <c r="V46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>10153100</v>
+      </c>
+      <c r="E47" s="3">
         <v>9905000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>8547300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>9068100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>9308400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>9766500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>8391200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>8642400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>8157400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>7163200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>341600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1373400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1269300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1045700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>281500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>236900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>222000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>203600</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
-      </c>
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1767500</v>
+      </c>
+      <c r="E48" s="3">
         <v>1430200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1368000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1720500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1462300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1543600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1512300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1467800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1422500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1565600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1736500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1781500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1831400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1680800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2184100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1943400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1863500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1891300</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
-      </c>
       <c r="V48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9187200</v>
+      </c>
+      <c r="E49" s="3">
         <v>4570500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8743800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9059700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9002400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9504600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9281000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4460400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4301500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3856100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4207500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4197300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4169400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3659200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5153000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4526400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4199400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4064600</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
-      </c>
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3101,8 +3215,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3163,70 +3280,76 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>131700</v>
+      </c>
+      <c r="E52" s="3">
         <v>442600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1055200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>128300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>394700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>415800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1242000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>398500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>407500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>131200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>466600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>34400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>37700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>35300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>473700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>31700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>26300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>52600</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
-      </c>
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3287,70 +3410,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>82208500</v>
+      </c>
+      <c r="E54" s="3">
         <v>78648100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>74351300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>76902800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>76549300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>79536600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>77744300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>73843200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>71426200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>64562300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>70941900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>71474100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>71788900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>62669800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>88056900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>77375100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>72292900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>70751400</v>
       </c>
-      <c r="U54" s="3">
-        <v>0</v>
-      </c>
       <c r="V54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3373,8 +3502,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3397,103 +3527,107 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>52837300</v>
+      </c>
+      <c r="E57" s="3">
         <v>49547900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>46291200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>47795300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>48699600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>49877100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>47873400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>45245700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>43193000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>38526900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>672900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>640100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>663800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>569900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>774800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>641300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>596400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>572900</v>
       </c>
-      <c r="U57" s="3">
-        <v>0</v>
-      </c>
       <c r="V57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4785800</v>
+      </c>
+      <c r="E58" s="3">
         <v>4344400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6318400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5349900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4078600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4814100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6612400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4524100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>447800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>329000</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -3521,103 +3655,109 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1801800</v>
+      </c>
+      <c r="E59" s="3">
         <v>72900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>542300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1920500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2125900</v>
       </c>
-      <c r="H59" s="3">
-        <v>2205100</v>
-      </c>
       <c r="I59" s="3">
+        <v>2068800</v>
+      </c>
+      <c r="J59" s="3">
         <v>695700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1980000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>28400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1201900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>224300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1462100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1427000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1298500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>387400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1382400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1246800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1332200</v>
       </c>
-      <c r="U59" s="3">
-        <v>0</v>
-      </c>
       <c r="V59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>59779100</v>
+      </c>
+      <c r="E60" s="3">
         <v>53965200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>53451400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>55270700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>55199400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>57188000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>55477600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>51909900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>43669300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>40057800</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -3645,132 +3785,141 @@
       <c r="V60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>12363400</v>
+      </c>
+      <c r="E61" s="3">
         <v>12255200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>10430800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>11919900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12113400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>12663900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>10918200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>12743000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>16037400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>15129400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>15126900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>14763300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>15120000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>12389300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>15026400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>12193300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>11352000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>11073300</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>771500</v>
+      </c>
+      <c r="E62" s="3">
         <v>3049100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>563400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>518100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>502800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>512700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>759600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>567900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2838100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2654000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1621000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>390900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>404600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>393900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1462300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>348700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>332700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>339500</v>
       </c>
-      <c r="U62" s="3">
-        <v>0</v>
-      </c>
       <c r="V62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3831,8 +3980,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3893,8 +4045,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3955,70 +4110,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>73968000</v>
+      </c>
+      <c r="E66" s="3">
         <v>70867300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>66830700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>69037700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>68890100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>71482700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>69607900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>66241000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>64054500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>58032800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>66989800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>67282400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>67519700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>58774500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>82533700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>72460600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>67787200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>66472500</v>
       </c>
-      <c r="U66" s="3">
-        <v>0</v>
-      </c>
       <c r="V66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4041,8 +4202,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4103,8 +4265,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4165,8 +4330,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4227,8 +4395,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4289,70 +4460,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E72" s="3">
+      <c r="D72" s="3">
+        <v>2048300</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F72" s="3">
         <v>1851300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1893300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1808900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1886400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1995800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1888900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1817500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1604700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1924400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2087700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2065500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2032800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3212000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2777700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2486200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2287600</v>
       </c>
-      <c r="U72" s="3">
-        <v>0</v>
-      </c>
       <c r="V72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4413,8 +4590,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4475,8 +4655,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4537,70 +4720,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4349100</v>
+      </c>
+      <c r="E76" s="3">
         <v>4094600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3957600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4170300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4042400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4263900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4332100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4049300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3945700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3494200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3952100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4191600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4269200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3895300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5523300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4914500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4505700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4279000</v>
       </c>
-      <c r="U76" s="3">
-        <v>0</v>
-      </c>
       <c r="V76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4661,137 +4850,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>121200</v>
+      </c>
+      <c r="E81" s="3">
         <v>86200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>63800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>99700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>49400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>29500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>21400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>16000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>39800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>91800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-102500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>102000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>175600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>415100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-36100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>171500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>199400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>166300</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4814,70 +5012,74 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E83" s="3">
         <v>78300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>36500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>34300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>67700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>60400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>29200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>58900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>64900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>70100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>68600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>67700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>70400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>63200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>89100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>80700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>73900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>74800</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
-      </c>
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4938,8 +5140,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5000,8 +5205,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5062,8 +5270,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5124,8 +5335,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5186,70 +5400,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E89" s="3">
+      <c r="E89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F89" s="3">
         <v>-678600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>203900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1846100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1105100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-345700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>88800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-847100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1043600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-998500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-333000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1538000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-489300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>495500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-21700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>505500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>321100</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
       <c r="V89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5272,70 +5492,74 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E91" s="3">
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3">
         <v>-47700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-31500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-42200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-38000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-59700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-33700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-37900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-19400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-482508000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-281054000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-238582000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-143769000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-489803000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-299606000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-24200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-16300</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5396,8 +5620,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5458,70 +5685,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E94" s="3">
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3">
         <v>-635700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>242200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>101900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-458700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-19300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-228900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>54900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>564200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>662200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>345800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>47900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4161400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-522800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>67100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-178900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-814100</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5544,70 +5777,74 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E96" s="3">
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3">
         <v>43100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>33900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>34200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>66100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>65800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>63000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>61100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-28600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-72000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-72100</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-66000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-62900</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-69500</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5668,8 +5905,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5730,8 +5970,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5792,132 +6035,141 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E100" s="3">
+      <c r="E100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="3">
         <v>658300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-523100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1660900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1521100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>808000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-27500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>934200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1058000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-573100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1186700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-276100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-89700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-18500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-57600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-229100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>17700</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>259300</v>
+      </c>
+      <c r="E101" s="3">
         <v>35100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-387300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-33400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-173700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-82900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>579300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>275700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-128900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>673900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>317100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-116100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>226000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>73500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>3600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>707700</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5925,57 +6177,60 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-488300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-34600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>176000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-7700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>55600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-201100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-31700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>495800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-235500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-856800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1308800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-4856600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>180100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>61300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>101100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>232400</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
       <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AVAL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AVAL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="92">
   <si>
     <t>AVAL</t>
   </si>
@@ -656,175 +656,181 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="20" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="21" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>939700</v>
+      </c>
+      <c r="E8" s="3">
         <v>890600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>865700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>815400</v>
       </c>
-      <c r="G8" s="3">
-        <v>676400</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3">
         <v>748900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>690000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>720200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>694700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>604100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>701300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>789000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1474500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1303200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1114500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>902300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>578700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>707300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>660300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>653500</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -891,47 +897,50 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>939700</v>
+      </c>
+      <c r="E10" s="3">
         <v>890600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>865700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>815400</v>
       </c>
-      <c r="G10" s="3">
-        <v>676400</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="H10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="3">
         <v>748900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>690000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>720200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>694700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>604100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>701300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>789000</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
@@ -959,8 +968,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -985,8 +997,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1053,8 +1066,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1121,44 +1137,47 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E14" s="3">
         <v>-4700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-3400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-1900</v>
       </c>
-      <c r="G14" s="3">
-        <v>1800</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>-2400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-4100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-2100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-23300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-3500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>7100</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
@@ -1183,82 +1202,88 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>67700</v>
+      </c>
+      <c r="E15" s="3">
         <v>72600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>66600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>59500</v>
       </c>
-      <c r="G15" s="3">
-        <v>60100</v>
-      </c>
       <c r="H15" s="3">
+        <v>53700</v>
+      </c>
+      <c r="I15" s="3">
         <v>61900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>42000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>78300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>61100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>55900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>38500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>60400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-68600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-67700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-70400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-63200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-62600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-57200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-52400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-52900</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1280,144 +1305,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>639100</v>
+      </c>
+      <c r="E17" s="3">
         <v>539800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>524100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>503600</v>
       </c>
-      <c r="G17" s="3">
-        <v>509200</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="H17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" s="3">
         <v>465800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>482000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>510900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>545600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>461800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>468700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>415300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1207500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>968100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>748600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>569900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>251700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>364100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>387300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>404100</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>300700</v>
+      </c>
+      <c r="E18" s="3">
         <v>350800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>341600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>311800</v>
       </c>
-      <c r="G18" s="3">
-        <v>167300</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="H18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="3">
         <v>283100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>208000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>209300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>149100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>142200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>232500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>373700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>266900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>335100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>366000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>332400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>326900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>343200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>273000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>249400</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1442,144 +1474,151 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
         <v>37900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>34600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>32300</v>
       </c>
-      <c r="G20" s="3">
-        <v>28600</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3">
         <v>28500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>27400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>30200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>12400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>27900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>31100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>32500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-67700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>34200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>141100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>151400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-32600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>58500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>91300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>81900</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>368400</v>
+      </c>
+      <c r="E21" s="3">
         <v>385500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>373600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>339100</v>
       </c>
-      <c r="G21" s="3">
-        <v>198800</v>
-      </c>
       <c r="H21" s="3">
+        <v>53700</v>
+      </c>
+      <c r="I21" s="3">
         <v>316400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>222600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>257300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>197800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>170200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>239900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>401700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>267800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>437100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>577500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>547100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>383500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>482300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>438200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>406100</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1616,8 +1655,8 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1640,150 +1679,159 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>3</v>
+      <c r="W22" s="3">
+        <v>0</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>309500</v>
+      </c>
+      <c r="E23" s="3">
         <v>317600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>310400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>281400</v>
       </c>
-      <c r="G23" s="3">
-        <v>136900</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="H23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I23" s="3">
         <v>256900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>184800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>181100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>160000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>117900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>194400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>341300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>199300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>369400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>507100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>483900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>294300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>401700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>364300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>331300</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>90100</v>
+      </c>
+      <c r="E24" s="3">
         <v>90700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>94000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>90400</v>
       </c>
-      <c r="G24" s="3">
-        <v>14300</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3">
         <v>82100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>76200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>58500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>64800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>43600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>84000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>115000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>126300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>137000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>146700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>151900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>91000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>222600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>92500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>103300</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1850,144 +1898,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>219400</v>
+      </c>
+      <c r="E26" s="3">
         <v>226900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>216400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>191100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26" s="3">
+        <v>174800</v>
+      </c>
+      <c r="J26" s="3">
+        <v>108600</v>
+      </c>
+      <c r="K26" s="3">
         <v>122600</v>
       </c>
-      <c r="H26" s="3">
-        <v>174800</v>
-      </c>
-      <c r="I26" s="3">
-        <v>108600</v>
-      </c>
-      <c r="J26" s="3">
-        <v>122600</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>95100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>74300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>110400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>226200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>72900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>232400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>360400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>332000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>203300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>179100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>271800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>228000</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>91300</v>
+      </c>
+      <c r="E27" s="3">
         <v>132600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>121200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>86200</v>
       </c>
-      <c r="G27" s="3">
-        <v>63800</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="H27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I27" s="3">
         <v>99700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>49400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>29500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>21400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>16000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>39800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>91800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>95700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>102000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>175600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>151600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>37000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>111600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>138700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>204000</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2054,13 +2111,16 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>-50000</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
@@ -2093,37 +2153,40 @@
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>-198200</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
       <c r="Q29" s="3">
         <v>0</v>
       </c>
       <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
         <v>263500</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-73000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>59900</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>60700</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-37700</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2190,8 +2253,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2258,144 +2324,153 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
         <v>-37900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-34600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-32300</v>
       </c>
-      <c r="G32" s="3">
-        <v>-28600</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3">
         <v>-28500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-27400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-30200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-12400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-27900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-31100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-32500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>67700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-34200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-141100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-151400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>32600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-58500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-91300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-81900</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>91300</v>
+      </c>
+      <c r="E33" s="3">
         <v>132600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>121200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>86200</v>
       </c>
-      <c r="G33" s="3">
-        <v>63800</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="H33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I33" s="3">
         <v>99700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>49400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>29500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>21400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>16000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>39800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>91800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-102500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>102000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>175600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>415100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-36100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>171500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>199400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>166300</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2462,149 +2537,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>91300</v>
+      </c>
+      <c r="E35" s="3">
         <v>132600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>121200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>86200</v>
       </c>
-      <c r="G35" s="3">
-        <v>63800</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="H35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I35" s="3">
         <v>99700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>49400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>29500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>21400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>16000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>39800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>91800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-102500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>102000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>175600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>415100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-36100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>171500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>199400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>166300</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2629,8 +2713,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2655,183 +2740,190 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3624100</v>
+      </c>
+      <c r="E41" s="3">
         <v>4485400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4453300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4563300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1650700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4245300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4302400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4474400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2171600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4543900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4600000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4175100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4087900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4503500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5574700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3937700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8794300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7896300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7478900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7377700</v>
       </c>
-      <c r="W41" s="3">
-        <v>0</v>
-      </c>
       <c r="X41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>5471500</v>
+      </c>
+      <c r="E42" s="3">
         <v>7149900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>6050900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>4987800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3121600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>4870700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>4011700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>4002400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>3264500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>3206000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>3193300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2942300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>10928800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>11025600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>11083300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>9948200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>13366900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>11815200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>11196400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>10964900</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
-      </c>
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2500000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3290400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3367500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7071500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2489200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3173600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3191500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3210800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2488500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6990700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6681600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6018200</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
       <c r="P43" s="3">
         <v>0</v>
       </c>
@@ -2859,13 +2951,16 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>3</v>
+      <c r="D44" s="3">
+        <v>11700</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>3</v>
@@ -2873,32 +2968,32 @@
       <c r="F44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3">
         <v>17700</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3">
         <v>16600</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -2927,47 +3022,50 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7359900</v>
+      </c>
+      <c r="E45" s="3">
         <v>22400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>16500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>22700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1667000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>20900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>22300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>26700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>942400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>23300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>28200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>21600</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
       <c r="P45" s="3">
         <v>0</v>
       </c>
@@ -2995,47 +3093,50 @@
       <c r="X45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>20476100</v>
+      </c>
+      <c r="E46" s="3">
         <v>15064500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13998200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>16645300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>11150500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12659000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11890800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>12052200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11512700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>14763900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>14503000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>13157200</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -3063,212 +3164,224 @@
       <c r="X46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>9978400</v>
+      </c>
+      <c r="E47" s="3">
         <v>11016000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>10153100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>9905000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>8547300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>9068100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>9308400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>9766500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>8391200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>8642400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>8157400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>7163200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>341600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1373400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1269300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1045700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>281500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>236900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>222000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>203600</v>
       </c>
-      <c r="W47" s="3">
-        <v>0</v>
-      </c>
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2251500</v>
+      </c>
+      <c r="E48" s="3">
         <v>1815600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1767500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1430200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1368000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1720500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1462300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1543600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1512300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1467800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1422500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1565600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1736500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1781500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1831400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1680800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2184100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1943400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1863500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1891300</v>
       </c>
-      <c r="W48" s="3">
-        <v>0</v>
-      </c>
       <c r="X48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9434100</v>
+      </c>
+      <c r="E49" s="3">
         <v>9626000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9187200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4570500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8743800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9059700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9002400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9504600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9281000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4460400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4301500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3856100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4207500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4197300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4169400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3659200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5153000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4526400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4199400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4064600</v>
       </c>
-      <c r="W49" s="3">
-        <v>0</v>
-      </c>
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3335,8 +3448,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3403,76 +3519,82 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1179200</v>
+      </c>
+      <c r="E52" s="3">
         <v>137500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>131700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>442600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1055200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>128300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>394700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>415800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1242000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>398500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>407500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>131200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>466600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>34400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>37700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>35300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>473700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>31700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>26300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>52600</v>
       </c>
-      <c r="W52" s="3">
-        <v>0</v>
-      </c>
       <c r="X52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3539,76 +3661,82 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>92539000</v>
+      </c>
+      <c r="E54" s="3">
         <v>87509100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>82208500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>78648100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>74351300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>76902800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>76549300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>79536600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>77744300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>73843200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>71426200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>64562300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>70941900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>71474100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>71788900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>62669800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>88056900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>77375100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>72292900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>70751400</v>
       </c>
-      <c r="W54" s="3">
-        <v>0</v>
-      </c>
       <c r="X54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3633,8 +3761,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3659,115 +3788,119 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>55937600</v>
+      </c>
+      <c r="E57" s="3">
         <v>55028900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>52837300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>49547900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>46291200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>47795300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>48699600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>49877100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>47873400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>45245700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>43193000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>38526900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>672900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>640100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>663800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>569900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>774800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>641300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>596400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>572900</v>
       </c>
-      <c r="W57" s="3">
-        <v>0</v>
-      </c>
       <c r="X57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>9371200</v>
+      </c>
+      <c r="E58" s="3">
         <v>6820100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4785800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4344400</v>
       </c>
-      <c r="G58" s="3">
-        <v>6318400</v>
-      </c>
       <c r="H58" s="3">
+        <v>6318300</v>
+      </c>
+      <c r="I58" s="3">
         <v>5349900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4078600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4814100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6612400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4524100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>447800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>329000</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -3795,115 +3928,121 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4985500</v>
+      </c>
+      <c r="E59" s="3">
         <v>1798000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1801800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>72900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>542300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1920500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2125900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2068800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>695700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1980000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>28400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1201900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>224300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1462100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1427000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1298500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>387400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1382400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1246800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1332200</v>
       </c>
-      <c r="W59" s="3">
-        <v>0</v>
-      </c>
       <c r="X59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>70630900</v>
+      </c>
+      <c r="E60" s="3">
         <v>64017000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>59779100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>53965200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>53451400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>55270700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>55199400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>57188000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>55477600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>51909900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>43669300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>40057800</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -3931,144 +4070,153 @@
       <c r="X60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9367500</v>
+      </c>
+      <c r="E61" s="3">
         <v>12922500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>12363400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>12255200</v>
       </c>
-      <c r="G61" s="3">
-        <v>10430800</v>
-      </c>
       <c r="H61" s="3">
+        <v>10430900</v>
+      </c>
+      <c r="I61" s="3">
         <v>11919900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12113400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>12663900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10918200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>12743000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>16037400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>15129400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>15126900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>14763300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>15120000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>12389300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>15026400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>12193300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>11352000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>11073300</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>692400</v>
+      </c>
+      <c r="E62" s="3">
         <v>610500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>771500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3049100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>563400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>518100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>502800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>512700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>759600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>567900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2838100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2654000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1621000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>390900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>404600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>393900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1462300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>348700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>332700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>339500</v>
       </c>
-      <c r="W62" s="3">
-        <v>0</v>
-      </c>
       <c r="X62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4135,8 +4283,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4203,8 +4354,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4271,76 +4425,82 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>83325100</v>
+      </c>
+      <c r="E66" s="3">
         <v>78694100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>73968000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>70867300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>66830700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>69037700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>68890100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>71482700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>69607900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>66241000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>64054500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>58032800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>66989800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>67282400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>67519700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>58774500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>82533700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>72460600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>67787200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>66472500</v>
       </c>
-      <c r="W66" s="3">
-        <v>0</v>
-      </c>
       <c r="X66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4365,8 +4525,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4433,8 +4594,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4501,8 +4665,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4569,8 +4736,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4637,76 +4807,82 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2450800</v>
+      </c>
+      <c r="E72" s="3">
         <v>2266200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2048300</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H72" s="3">
         <v>1851300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1893300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1808900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1886400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1995800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1888900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1817500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1604700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1924400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2087700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2065500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2032800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>3212000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2777700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2486200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2287600</v>
       </c>
-      <c r="W72" s="3">
-        <v>0</v>
-      </c>
       <c r="X72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4773,8 +4949,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4841,8 +5020,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4909,76 +5091,82 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4891900</v>
+      </c>
+      <c r="E76" s="3">
         <v>4685700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4349100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4094600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3957600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4170300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4042400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4263900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4332100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4049300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3945700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3494200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3952100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4191600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4269200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3895300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5523300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4914500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4505700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4279000</v>
       </c>
-      <c r="W76" s="3">
-        <v>0</v>
-      </c>
       <c r="X76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5045,149 +5233,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>91300</v>
+      </c>
+      <c r="E81" s="3">
         <v>132600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>121200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>86200</v>
       </c>
-      <c r="G81" s="3">
-        <v>63800</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="H81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I81" s="3">
         <v>99700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>49400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>29500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>21400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>16000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>39800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>91800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-102500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>102000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>175600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>415100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-36100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>171500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>199400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>166300</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5212,76 +5409,80 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3">
         <v>78000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>75000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>78300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>36500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>34300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>67700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>60400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>29200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>58900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>64900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>70100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>68600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>67700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>70400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>63200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>89100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>80700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>73900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>74800</v>
       </c>
-      <c r="W83" s="3">
-        <v>0</v>
-      </c>
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5348,8 +5549,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5416,8 +5620,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5484,8 +5691,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5552,8 +5762,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5620,76 +5833,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" s="3">
         <v>-89200</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G89" s="3">
-        <v>-678600</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="G89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I89" s="3">
         <v>203900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1846100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1105100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-345700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>88800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-847100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1043600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-998500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-333000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1538000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-489300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>495500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-21700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>505500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>321100</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
       <c r="X89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5714,76 +5933,80 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3">
         <v>-36400</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G91" s="3">
-        <v>-47700</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3">
         <v>-31500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-42200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-38000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-59700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-33700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-37900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-19400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-482508000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-281054000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-238582000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-143769000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-489803000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-299606000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-24200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-16300</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5850,8 +6073,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5918,76 +6144,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3">
         <v>-369900</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G94" s="3">
-        <v>-635700</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3">
         <v>242200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>101900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-458700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-19300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-228900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>54900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>564200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>662200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>345800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>47900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4161400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-522800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>67100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-178900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-814100</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6012,76 +6244,80 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3">
         <v>41100</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G96" s="3">
-        <v>43100</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3">
         <v>33900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>34200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>66100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>65800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>63000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>61100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-600</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-28600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-72000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-72100</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-66000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-62900</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-69500</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6148,8 +6384,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6216,8 +6455,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6284,208 +6526,220 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3">
         <v>460300</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G100" s="3">
-        <v>658300</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3">
         <v>-523100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1660900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1521100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>808000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-27500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>934200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1058000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-573100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1186700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-276100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-89700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-18500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-57600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-229100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>17700</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3">
         <v>42300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>259300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>35100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-387300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-33400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-173700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-82900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>579300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>275700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-128900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>673900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>317100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-116100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>226000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>73500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>3600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>707700</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-140700</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
         <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>-488300</v>
+        <v>0</v>
       </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-34600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>176000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-7700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>55600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-201100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-31700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>495800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-235500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-856800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1308800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-4856600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>180100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>61300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>101100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>232400</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AVAL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AVAL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="92">
   <si>
     <t>AVAL</t>
   </si>
@@ -656,181 +656,188 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="21" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="22" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1062500</v>
+      </c>
+      <c r="E8" s="3">
         <v>939700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>890600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>865700</v>
       </c>
-      <c r="G8" s="3">
-        <v>815400</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="H8" s="3">
+        <v>779100</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3">
         <v>748900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>690000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>720200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>694700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>604100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>701300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>789000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1474500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1303200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1114500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>902300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>578700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>707300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>660300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>653500</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -900,50 +907,53 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1062500</v>
+      </c>
+      <c r="E10" s="3">
         <v>939700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>890600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>865700</v>
       </c>
-      <c r="G10" s="3">
-        <v>815400</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="H10" s="3">
+        <v>779100</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="3">
         <v>748900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>690000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>720200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>694700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>604100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>701300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>789000</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -971,8 +981,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -998,8 +1011,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1069,8 +1083,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1140,47 +1157,50 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E14" s="3">
         <v>-8800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-4700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-3400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-1900</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>-2400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-4100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-2100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-23300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-3500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>7100</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
@@ -1205,85 +1225,91 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>77900</v>
+      </c>
+      <c r="E15" s="3">
         <v>67700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>72600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>66600</v>
       </c>
-      <c r="G15" s="3">
-        <v>59500</v>
-      </c>
       <c r="H15" s="3">
+        <v>61600</v>
+      </c>
+      <c r="I15" s="3">
         <v>53700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>61900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>42000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>78300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>61100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>55900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>38500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>60400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-68600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-67700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-70400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-63200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-62600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-57200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-52400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-52900</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1306,150 +1332,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>656700</v>
+      </c>
+      <c r="E17" s="3">
         <v>639100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>539800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>524100</v>
       </c>
-      <c r="G17" s="3">
-        <v>503600</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="H17" s="3">
+        <v>477900</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J17" s="3">
         <v>465800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>482000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>510900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>545600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>461800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>468700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>415300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1207500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>968100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>748600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>569900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>251700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>364100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>387300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>404100</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>405800</v>
+      </c>
+      <c r="E18" s="3">
         <v>300700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>350800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>341600</v>
       </c>
-      <c r="G18" s="3">
-        <v>311800</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="H18" s="3">
+        <v>301200</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3">
         <v>283100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>208000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>209300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>149100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>142200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>232500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>373700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>266900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>335100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>366000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>332400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>326900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>343200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>273000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>249400</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1475,150 +1508,157 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="D20" s="3">
+        <v>40300</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3">
         <v>37900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>34600</v>
       </c>
-      <c r="G20" s="3">
-        <v>32300</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="H20" s="3">
         <v>28500</v>
       </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="J20" s="3">
+        <v>28500</v>
+      </c>
+      <c r="K20" s="3">
         <v>27400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>30200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>12400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>27900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>31100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>32500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-67700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>34200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>141100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>151400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-32600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>58500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>91300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>81900</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>443400</v>
+      </c>
+      <c r="E21" s="3">
         <v>368400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>385500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>373600</v>
       </c>
-      <c r="G21" s="3">
-        <v>339100</v>
-      </c>
       <c r="H21" s="3">
+        <v>334300</v>
+      </c>
+      <c r="I21" s="3">
         <v>53700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>316400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>222600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>257300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>197800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>170200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>239900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>401700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>267800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>437100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>577500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>547100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>383500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>482300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>438200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>406100</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1658,8 +1698,8 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1682,156 +1722,165 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>3</v>
+      <c r="X22" s="3">
+        <v>0</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>367600</v>
+      </c>
+      <c r="E23" s="3">
         <v>309500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>317600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>310400</v>
       </c>
-      <c r="G23" s="3">
-        <v>281400</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="H23" s="3">
+        <v>274500</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J23" s="3">
         <v>256900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>184800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>181100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>160000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>117900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>194400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>341300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>199300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>369400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>507100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>483900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>294300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>401700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>364300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>331300</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>157800</v>
+      </c>
+      <c r="E24" s="3">
         <v>90100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>90700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>94000</v>
       </c>
-      <c r="G24" s="3">
-        <v>90400</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="H24" s="3">
+        <v>89400</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3">
         <v>82100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>76200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>58500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>64800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>43600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>84000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>115000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>126300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>137000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>146700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>151900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>91000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>222600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>92500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>103300</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1901,150 +1950,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>209900</v>
+      </c>
+      <c r="E26" s="3">
         <v>219400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>226900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>216400</v>
       </c>
-      <c r="G26" s="3">
-        <v>191100</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="H26" s="3">
+        <v>185200</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J26" s="3">
         <v>174800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>108600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>122600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>95100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>74300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>110400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>226200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>72900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>232400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>360400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>332000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>203300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>179100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>271800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>228000</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>91900</v>
+      </c>
+      <c r="E27" s="3">
         <v>91300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>132600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>121200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>86200</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="I27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J27" s="3">
         <v>99700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>49400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>29500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>21400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>16000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>39800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>91800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>95700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>102000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>175600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>151600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>37000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>111600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>138700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>204000</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2114,17 +2172,20 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E29" s="3">
         <v>-50000</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
       <c r="F29" s="3">
         <v>0</v>
       </c>
@@ -2132,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>5900</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
@@ -2156,37 +2217,40 @@
         <v>0</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>-198200</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
       <c r="R29" s="3">
         <v>0</v>
       </c>
       <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
         <v>263500</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-73000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>59900</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>60700</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-37700</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2256,8 +2320,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2327,150 +2394,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" s="3">
+      <c r="D32" s="3">
+        <v>-40300</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3">
         <v>-37900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-34600</v>
       </c>
-      <c r="G32" s="3">
-        <v>-32300</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="H32" s="3">
         <v>-28500</v>
       </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="J32" s="3">
+        <v>-28500</v>
+      </c>
+      <c r="K32" s="3">
         <v>-27400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-30200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-12400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-27900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-31100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-32500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>67700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-34200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-141100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-151400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>32600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-58500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-91300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-81900</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>91900</v>
+      </c>
+      <c r="E33" s="3">
         <v>91300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>132600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>121200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>86200</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="I33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J33" s="3">
         <v>99700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>49400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>29500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>21400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>16000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>39800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>91800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-102500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>102000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>175600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>415100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-36100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>171500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>199400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>166300</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2540,155 +2616,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>91900</v>
+      </c>
+      <c r="E35" s="3">
         <v>91300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>132600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>121200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>86200</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="I35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J35" s="3">
         <v>99700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>49400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>29500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>21400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>16000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>39800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>91800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-102500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>102000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>175600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>415100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-36100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>171500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>199400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>166300</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2714,8 +2799,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2741,192 +2827,199 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4477200</v>
+      </c>
+      <c r="E41" s="3">
         <v>3624100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4485400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4453300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4563300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1650700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4245300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4302400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4474400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2171600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4543900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4600000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4175100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4087900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4503500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5574700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3937700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8794300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7896300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7478900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7377700</v>
       </c>
-      <c r="X41" s="3">
-        <v>0</v>
-      </c>
       <c r="Y41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>7921500</v>
+      </c>
+      <c r="E42" s="3">
         <v>5471500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>7149900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>6050900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>4987800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3121600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>4870700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>4011700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4002400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>3264500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>3206000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>3193300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2942300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>10928800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>11025600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>11083300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>9948200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>13366900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>11815200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>11196400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>10964900</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
-      </c>
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3430100</v>
+      </c>
+      <c r="E43" s="3">
         <v>2500000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3290400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3367500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7071500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2489200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3173600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3191500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3210800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2488500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6990700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6681600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6018200</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
       <c r="Q43" s="3">
         <v>0</v>
       </c>
@@ -2954,49 +3047,52 @@
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E44" s="3">
         <v>11700</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3">
         <v>17700</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3">
         <v>16600</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3025,50 +3121,53 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E45" s="3">
         <v>7359900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>22400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>16500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>22700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1667000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>20900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>22300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>26700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>942400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>23300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>28200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>21600</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3">
         <v>0</v>
       </c>
@@ -3096,50 +3195,53 @@
       <c r="Y45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>17849600</v>
+      </c>
+      <c r="E46" s="3">
         <v>20476100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>15064500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>13998200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>16645300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11150500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12659000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11890800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>12052200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11512700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>14763900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>14503000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>13157200</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -3167,221 +3269,233 @@
       <c r="Y46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>10838700</v>
+      </c>
+      <c r="E47" s="3">
         <v>9978400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>11016000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>10153100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>9905000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>8547300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>9068100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>9308400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>9766500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>8391200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>8642400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>8157400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>7163200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>341600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1373400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1269300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1045700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>281500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>236900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>222000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>203600</v>
       </c>
-      <c r="X47" s="3">
-        <v>0</v>
-      </c>
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2628900</v>
+      </c>
+      <c r="E48" s="3">
         <v>2251500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1815600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1767500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1430200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1368000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1720500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1462300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1543600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1512300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1467800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1422500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1565600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1736500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1781500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1831400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1680800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2184100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1943400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1863500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1891300</v>
       </c>
-      <c r="X48" s="3">
-        <v>0</v>
-      </c>
       <c r="Y48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9765700</v>
+      </c>
+      <c r="E49" s="3">
         <v>9434100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9626000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9187200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4570500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8743800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9059700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9002400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9504600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9281000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4460400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4301500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3856100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4207500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4197300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4169400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3659200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5153000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4526400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4199400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4064600</v>
       </c>
-      <c r="X49" s="3">
-        <v>0</v>
-      </c>
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3451,8 +3565,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3522,79 +3639,85 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>109000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1179200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>137500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>131700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>442600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1055200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>128300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>394700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>415800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1242000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>398500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>407500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>131200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>466600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>34400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>37700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>35300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>473700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>31700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>26300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>52600</v>
       </c>
-      <c r="X52" s="3">
-        <v>0</v>
-      </c>
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3664,79 +3787,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>92227100</v>
+      </c>
+      <c r="E54" s="3">
         <v>92539000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>87509100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>82208500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>78648100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>74351300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>76902800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>76549300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>79536600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>77744300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>73843200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>71426200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>64562300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>70941900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>71474100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>71788900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>62669800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>88056900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>77375100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>72292900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>70751400</v>
       </c>
-      <c r="X54" s="3">
-        <v>0</v>
-      </c>
       <c r="Y54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3762,8 +3891,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3789,121 +3919,125 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>60188700</v>
+      </c>
+      <c r="E57" s="3">
         <v>55937600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>55028900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>52837300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>49547900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>46291200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>47795300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>48699600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>49877100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>47873400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>45245700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>43193000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>38526900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>672900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>640100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>663800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>569900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>774800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>641300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>596400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>572900</v>
       </c>
-      <c r="X57" s="3">
-        <v>0</v>
-      </c>
       <c r="Y57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6334200</v>
+      </c>
+      <c r="E58" s="3">
         <v>9371200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6820100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4785800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4344400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6318300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5349900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4078600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4814100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6612400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4524100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>447800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>329000</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -3931,121 +4065,127 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2566500</v>
+      </c>
+      <c r="E59" s="3">
         <v>4985500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1798000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1801800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>72900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>542300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1920500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2125900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2068800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>695700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1980000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>28400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1201900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>224300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1462100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1427000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1298500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>387400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1382400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1246800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1332200</v>
       </c>
-      <c r="X59" s="3">
-        <v>0</v>
-      </c>
       <c r="Y59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>69330500</v>
+      </c>
+      <c r="E60" s="3">
         <v>70630900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>64017000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>59779100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>53965200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>53451400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>55270700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>55199400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>57188000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>55477600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>51909900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>43669300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>40057800</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -4073,150 +4213,159 @@
       <c r="Y60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>11838500</v>
+      </c>
+      <c r="E61" s="3">
         <v>9367500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>12922500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>12363400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12255200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>10430900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>11919900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>12113400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>12663900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>10918200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>12743000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>16037400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>15129400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>15126900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>14763300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>15120000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>12389300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>15026400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>12193300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>11352000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>11073300</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>635400</v>
+      </c>
+      <c r="E62" s="3">
         <v>692400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>610500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>771500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3049100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>563400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>518100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>502800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>512700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>759600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>567900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2838100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2654000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1621000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>390900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>404600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>393900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1462300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>348700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>332700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>339500</v>
       </c>
-      <c r="X62" s="3">
-        <v>0</v>
-      </c>
       <c r="Y62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4286,8 +4435,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4357,8 +4509,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4428,79 +4583,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>83044600</v>
+      </c>
+      <c r="E66" s="3">
         <v>83325100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>78694100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>73968000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>70867300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>66830700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>69037700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>68890100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>71482700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>69607900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>66241000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>64054500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>58032800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>66989800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>67282400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>67519700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>58774500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>82533700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>72460600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>67787200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>66472500</v>
       </c>
-      <c r="X66" s="3">
-        <v>0</v>
-      </c>
       <c r="Y66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4526,8 +4687,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4597,8 +4759,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4668,8 +4833,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4739,8 +4907,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4810,79 +4981,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2411200</v>
+      </c>
+      <c r="E72" s="3">
         <v>2450800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2266200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2048300</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I72" s="3">
         <v>1851300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1893300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1808900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1886400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1995800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1888900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1817500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1604700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1924400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2087700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2065500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2032800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3212000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2777700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2486200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2287600</v>
       </c>
-      <c r="X72" s="3">
-        <v>0</v>
-      </c>
       <c r="Y72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4952,8 +5129,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5023,8 +5203,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5094,79 +5277,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4862400</v>
+      </c>
+      <c r="E76" s="3">
         <v>4891900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4685700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4349100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4094600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3957600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4170300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4042400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4263900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4332100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4049300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3945700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3494200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3952100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4191600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4269200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3895300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5523300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4914500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4505700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4279000</v>
       </c>
-      <c r="X76" s="3">
-        <v>0</v>
-      </c>
       <c r="Y76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5236,155 +5425,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>91900</v>
+      </c>
+      <c r="E81" s="3">
         <v>91300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>132600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>121200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>86200</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="I81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J81" s="3">
         <v>99700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>49400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>29500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>21400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>16000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>39800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>91800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-102500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>102000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>175600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>415100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-36100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>171500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>199400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>166300</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5410,79 +5608,83 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E83" s="3">
+      <c r="D83" s="3">
+        <v>34300</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3">
         <v>78000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>75000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>78300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>36500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>34300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>67700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>60400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>29200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>58900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>64900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>70100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>68600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>67700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>70400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>63200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>89100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>80700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>73900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>74800</v>
       </c>
-      <c r="X83" s="3">
-        <v>0</v>
-      </c>
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5552,8 +5754,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5623,8 +5828,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5694,8 +5902,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5765,8 +5976,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5836,79 +6050,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E89" s="3">
+      <c r="D89" s="3">
+        <v>-1074800</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F89" s="3">
         <v>-89200</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="H89" s="3">
+        <v>-1314000</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3">
         <v>203900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1846100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1105100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-345700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>88800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-847100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1043600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-998500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-333000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1538000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-489300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>495500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-21700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>505500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>321100</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
       <c r="Y89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5934,79 +6154,83 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E91" s="3">
+      <c r="D91" s="3">
+        <v>-27500</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3">
         <v>-36400</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I91" s="3">
+      <c r="H91" s="3">
+        <v>-30500</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3">
         <v>-31500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-42200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-38000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-59700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-33700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-37900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-19400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-482508000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-281054000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-238582000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-143769000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-489803000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-299606000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-24200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-16300</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6076,8 +6300,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6147,79 +6374,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E94" s="3">
+      <c r="D94" s="3">
+        <v>633800</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3">
         <v>-369900</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="H94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3">
         <v>242200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>101900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-458700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-19300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-228900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>54900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>564200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>662200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>345800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>47900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4161400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-522800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>67100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-178900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-814100</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6245,79 +6478,83 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E96" s="3">
+      <c r="D96" s="3">
+        <v>44100</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3">
         <v>41100</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I96" s="3">
+      <c r="H96" s="3">
+        <v>33600</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3">
         <v>33900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>34200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>66100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>65800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>63000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>61100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-28600</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-72000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-72100</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-66000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-62900</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-69500</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6387,8 +6624,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6458,8 +6698,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6529,217 +6772,229 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E100" s="3">
+      <c r="D100" s="3">
+        <v>1962700</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="3">
         <v>460300</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="H100" s="3">
+        <v>1961700</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3">
         <v>-523100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1660900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1521100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>808000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-27500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>934200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1058000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-573100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1186700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-276100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-89700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-18500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-57600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-229100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>17700</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E101" s="3">
+      <c r="D101" s="3">
+        <v>-136500</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3">
         <v>42300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>259300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>35100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-387300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-33400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-173700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-82900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>579300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>275700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-128900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>673900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>317100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-116100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>226000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>73500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>3600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>707700</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>1196300</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-140700</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
         <v>0</v>
       </c>
       <c r="H102" s="3">
-        <v>0</v>
+        <v>510200</v>
       </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-34600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>176000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-7700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>55600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-201100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-31700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>495800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-235500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-856800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1308800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-4856600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>180100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>61300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>101100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>232400</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
       <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
         <v>0</v>
       </c>
     </row>
